--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>1.82</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I5" t="n">
         <v>9.4</v>
@@ -1634,7 +1634,7 @@
         <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 02:11:20</t>
+          <t>2026-06-13 04:31:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 04:31:58</t>
+          <t>2026-06-13 06:52:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 06:52:19</t>
+          <t>2026-06-13 09:12:09</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 06:52:19</t>
+          <t>2026-06-13 09:12:09</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 06:52:19</t>
+          <t>2026-06-13 09:12:09</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 06:52:19</t>
+          <t>2026-06-13 09:12:09</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 06:52:19</t>
+          <t>2026-06-13 09:12:09</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>2.16</v>
       </c>
       <c r="G7" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 06:52:19</t>
+          <t>2026-06-13 09:12:09</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 06:52:19</t>
+          <t>2026-06-13 09:12:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -866,7 +866,7 @@
         <v>2.08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 09:12:09</t>
+          <t>2026-06-13 11:29:46</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 09:12:09</t>
+          <t>2026-06-13 11:29:46</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 09:12:09</t>
+          <t>2026-06-13 11:29:46</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G5" t="n">
         <v>1.82</v>
@@ -1628,7 +1628,7 @@
         <v>2.26</v>
       </c>
       <c r="I5" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
         <v>3.75</v>
@@ -1652,7 +1652,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 09:12:09</t>
+          <t>2026-06-13 11:29:46</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 09:12:09</t>
+          <t>2026-06-13 11:29:46</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 09:12:09</t>
+          <t>2026-06-13 11:29:46</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 09:12:09</t>
+          <t>2026-06-13 11:29:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G2" t="n">
         <v>3.75</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 11:29:46</t>
+          <t>2026-06-13 13:46:18</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 11:29:46</t>
+          <t>2026-06-13 13:46:18</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 11:29:46</t>
+          <t>2026-06-13 13:46:18</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="G5" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="H5" t="n">
-        <v>2.26</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 11:29:46</t>
+          <t>2026-06-13 13:46:18</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 11:29:46</t>
+          <t>2026-06-13 13:46:18</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 11:29:46</t>
+          <t>2026-06-13 13:46:18</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 11:29:46</t>
+          <t>2026-06-13 13:46:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G2" t="n">
         <v>3.75</v>
@@ -866,7 +866,7 @@
         <v>2.08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
@@ -875,16 +875,16 @@
         <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
         <v>2.16</v>
@@ -893,194 +893,194 @@
         <v>1.75</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 13:46:18</t>
+          <t>2026-06-13 16:02:15</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>2.36</v>
       </c>
       <c r="H3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I3" t="n">
         <v>3.55</v>
@@ -1129,16 +1129,16 @@
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
         <v>2.14</v>
@@ -1147,194 +1147,194 @@
         <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 13:46:18</t>
+          <t>2026-06-13 16:02:15</t>
         </is>
       </c>
     </row>
@@ -1383,16 +1383,16 @@
         <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
         <v>1.24</v>
@@ -1401,194 +1401,194 @@
         <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 13:46:18</t>
+          <t>2026-06-13 16:02:15</t>
         </is>
       </c>
     </row>
@@ -1625,13 +1625,13 @@
         <v>1.76</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
         <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
         <v>4.7</v>
@@ -1652,7 +1652,7 @@
         <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 13:46:18</t>
+          <t>2026-06-13 16:02:15</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 13:46:18</t>
+          <t>2026-06-13 16:02:15</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G7" t="n">
         <v>2.44</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 13:46:18</t>
+          <t>2026-06-13 16:02:15</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
         <v>3.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 13:46:18</t>
+          <t>2026-06-13 16:02:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G2" t="n">
         <v>3.75</v>
@@ -1076,11 +1076,11 @@
         <v>21</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>2.36</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I3" t="n">
         <v>3.55</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="O3" t="n">
         <v>1.24</v>
@@ -1147,7 +1147,7 @@
         <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
         <v>2.8</v>
@@ -1162,7 +1162,7 @@
         <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -1398,19 +1398,19 @@
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R4" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
         <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G7" t="n">
         <v>2.44</v>
@@ -2160,7 +2160,7 @@
         <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
         <v>3.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 16:02:15</t>
+          <t>2026-06-13 18:17:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -1028,7 +1028,7 @@
         <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>7</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BP2" t="n">
         <v>27</v>
@@ -1076,11 +1076,11 @@
         <v>21</v>
       </c>
       <c r="CA2" t="n">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 18:17:01</t>
+          <t>2026-06-13 20:32:09</t>
         </is>
       </c>
     </row>
@@ -1132,13 +1132,13 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.24</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
         <v>2.14</v>
@@ -1147,16 +1147,16 @@
         <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="U3" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="V3" t="n">
         <v>1.39</v>
@@ -1177,10 +1177,10 @@
         <v>80</v>
       </c>
       <c r="AB3" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>20</v>
@@ -1189,13 +1189,13 @@
         <v>42</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AG3" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
@@ -1213,128 +1213,128 @@
         <v>100</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.32</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.28</v>
+        <v>13.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.38</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.48</v>
+        <v>36</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.22</v>
+        <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.26</v>
+        <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.4</v>
+        <v>25</v>
       </c>
       <c r="AX3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>10</v>
       </c>
-      <c r="AY3" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>2.28</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.46</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
         <v>19.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.36</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.42</v>
+        <v>24</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.56</v>
+        <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.56</v>
+        <v>18</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.9</v>
+        <v>1.67</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BN3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BP3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BQ3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BT3" t="n">
         <v>9.6</v>
       </c>
-      <c r="BR3" t="n">
+      <c r="BU3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV3" t="n">
         <v>36</v>
       </c>
-      <c r="BS3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>34</v>
-      </c>
       <c r="BW3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY3" t="n">
         <v>1.84</v>
       </c>
-      <c r="BX3" t="n">
-        <v>46</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>1.87</v>
-      </c>
       <c r="BZ3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 18:17:01</t>
+          <t>2026-06-13 20:32:09</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.01</v>
@@ -1398,7 +1398,7 @@
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 18:17:01</t>
+          <t>2026-06-13 20:32:09</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>1.76</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="I5" t="n">
         <v>7.2</v>
@@ -1634,19 +1634,19 @@
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
         <v>2.14</v>
@@ -1655,194 +1655,194 @@
         <v>1.61</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 18:17:01</t>
+          <t>2026-06-13 20:32:09</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.28</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
@@ -1885,218 +1885,218 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="P6" t="n">
         <v>1.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 18:17:01</t>
+          <t>2026-06-13 20:32:09</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 18:17:01</t>
+          <t>2026-06-13 20:32:09</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
         <v>3.1</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 18:17:01</t>
+          <t>2026-06-13 20:32:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -983,7 +983,7 @@
         <v>7.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AW2" t="n">
         <v>18.5</v>
@@ -1064,7 +1064,7 @@
         <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX2" t="n">
         <v>26</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1186,7 +1186,7 @@
         <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF3" t="n">
         <v>16</v>
@@ -1198,10 +1198,10 @@
         <v>16.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK3" t="n">
         <v>32</v>
@@ -1219,7 +1219,7 @@
         <v>42</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3" t="n">
         <v>13.5</v>
@@ -1228,7 +1228,7 @@
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3" t="n">
         <v>10.5</v>
@@ -1264,7 +1264,7 @@
         <v>24</v>
       </c>
       <c r="BE3" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BF3" t="n">
         <v>12.5</v>
@@ -1273,68 +1273,68 @@
         <v>18</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.67</v>
+        <v>5.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.91</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.73</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
         <v>38</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.82</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW3" t="n">
         <v>9.6</v>
       </c>
-      <c r="BU3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>1.82</v>
-      </c>
       <c r="BX3" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.84</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.8</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -1885,40 +1885,40 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="O6" t="n">
         <v>1.05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Q6" t="n">
         <v>1.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
         <v>1.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.02</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2038,65 +2038,65 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -2145,16 +2145,16 @@
         <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P7" t="n">
         <v>1.45</v>
@@ -2163,194 +2163,194 @@
         <v>2.78</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -2399,212 +2399,212 @@
         <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="n">
         <v>2.12</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G2" t="n">
         <v>3.75</v>
@@ -866,16 +866,16 @@
         <v>2.08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -905,7 +905,7 @@
         <v>2.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="W2" t="n">
         <v>1.36</v>
@@ -983,7 +983,7 @@
         <v>7.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
         <v>18.5</v>
@@ -1064,7 +1064,7 @@
         <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
         <v>26</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 22:47:11</t>
+          <t>2026-06-14 01:01:34</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1.29</v>
@@ -1150,7 +1150,7 @@
         <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
         <v>1.66</v>
@@ -1162,7 +1162,7 @@
         <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
@@ -1276,7 +1276,7 @@
         <v>3.85</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BJ3" t="n">
         <v>9</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 22:47:11</t>
+          <t>2026-06-14 01:01:34</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 22:47:11</t>
+          <t>2026-06-14 01:01:34</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 22:47:11</t>
+          <t>2026-06-14 01:01:34</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 22:47:11</t>
+          <t>2026-06-14 01:01:34</t>
         </is>
       </c>
     </row>
@@ -2127,28 +2127,28 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="H7" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="J7" t="n">
         <v>2.86</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N7" t="n">
         <v>2.24</v>
@@ -2160,13 +2160,13 @@
         <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
         <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>2.78</v>
+        <v>6.2</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2175,10 +2175,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 22:47:11</t>
+          <t>2026-06-14 01:01:34</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,515 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-13 22:47:11</t>
+          <t>2026-06-14 01:01:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I9" t="n">
+        <v>110</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-14 01:01:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X10" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-14 01:01:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -1064,7 +1064,7 @@
         <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BX2" t="n">
         <v>26</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G3" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H3" t="n">
         <v>3.25</v>
@@ -1138,7 +1138,7 @@
         <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
         <v>2.14</v>
@@ -1219,7 +1219,7 @@
         <v>42</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>13.5</v>
@@ -1228,7 +1228,7 @@
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
         <v>10.5</v>
@@ -1264,7 +1264,7 @@
         <v>24</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
         <v>12.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>3.65</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
@@ -1652,7 +1652,7 @@
         <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
         <v>1.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1879,13 @@
         <v>1.28</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>
@@ -2139,25 +2139,25 @@
         <v>5.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K7" t="n">
         <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="O7" t="n">
         <v>1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q7" t="n">
         <v>2.74</v>
@@ -2169,10 +2169,10 @@
         <v>6.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="V7" t="n">
         <v>1.22</v>
@@ -2181,100 +2181,100 @@
         <v>1.8</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS7" t="n">
         <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW7" t="n">
         <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA7" t="n">
         <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD7" t="n">
         <v>1.01</v>
@@ -2283,74 +2283,74 @@
         <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG7" t="n">
         <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.55</v>
+        <v>5.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.55</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.55</v>
+        <v>6.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.55</v>
+        <v>4.6</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.55</v>
+        <v>9</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.55</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.55</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.14</v>
       </c>
       <c r="G8" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H8" t="n">
         <v>3.45</v>
@@ -2399,7 +2399,7 @@
         <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -2423,7 +2423,7 @@
         <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U8" t="n">
         <v>1.92</v>
@@ -2432,7 +2432,7 @@
         <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2441,7 +2441,7 @@
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
         <v>90</v>
@@ -2495,10 +2495,10 @@
         <v>3.75</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT8" t="n">
         <v>6.6</v>
@@ -2507,61 +2507,61 @@
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AY8" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.2</v>
       </c>
-      <c r="BA8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD8" t="n">
+      <c r="BG8" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.8</v>
       </c>
       <c r="BH8" t="n">
         <v>3.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BN8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BO8" t="n">
         <v>3.95</v>
@@ -2576,13 +2576,13 @@
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2594,17 +2594,17 @@
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>
@@ -2647,28 +2647,28 @@
         <v>110</v>
       </c>
       <c r="J9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
         <v>2.38</v>
       </c>
-      <c r="K9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.42</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P9" t="n">
         <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R9" t="n">
         <v>1.19</v>
@@ -2683,7 +2683,7 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
         <v>1.7</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>
@@ -2889,166 +2889,166 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G10" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="H10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N10" t="n">
         <v>2.94</v>
       </c>
-      <c r="I10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="O10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S10" t="n">
         <v>4.6</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.7</v>
-      </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="X10" t="n">
         <v>970</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.06</v>
+        <v>5.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.06</v>
+        <v>3.85</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.06</v>
+        <v>5.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.06</v>
+        <v>5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.06</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.06</v>
+        <v>6.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.06</v>
+        <v>10</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.06</v>
+        <v>6.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.06</v>
+        <v>6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.06</v>
+        <v>5.7</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.06</v>
+        <v>2.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.06</v>
+        <v>3.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.06</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.06</v>
+        <v>2.76</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.06</v>
+        <v>8.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.06</v>
+        <v>3.7</v>
       </c>
       <c r="BH10" t="n">
         <v>3.45</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-14 01:01:34</t>
+          <t>2026-06-14 03:16:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 03:16:20</t>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>
@@ -1129,13 +1129,13 @@
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.26</v>
@@ -1147,7 +1147,7 @@
         <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
         <v>2.88</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 03:16:20</t>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 03:16:20</t>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,36 +1605,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>1.76</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.24</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.4</v>
-      </c>
       <c r="S5" t="n">
-        <v>2.68</v>
+        <v>1.12</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1667,10 +1667,10 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 03:16:20</t>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,33 +1859,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
-        <v>1.28</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,19 +1897,19 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
         <v>1.05</v>
@@ -1921,7 +1921,7 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 03:16:20</t>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,168 +2113,168 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="G7" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="I7" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.58</v>
+        <v>1.02</v>
       </c>
       <c r="P7" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.74</v>
+        <v>1.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>6.2</v>
+        <v>1.02</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
         <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
         <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
         <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
         <v>1.01</v>
@@ -2283,74 +2283,74 @@
         <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
         <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-14 03:16:20</t>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Maranhao</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P8" t="n">
         <v>2.14</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.7</v>
-      </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2.68</v>
       </c>
       <c r="T8" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-14 03:16:20</t>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="H9" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>110</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
         <v>2.38</v>
       </c>
       <c r="O9" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.18</v>
+        <v>2.74</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
         <v>10</v>
       </c>
-      <c r="AC9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-14 03:16:20</t>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,111 +2875,111 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="G10" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="H10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I10" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
         <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="X10" t="n">
         <v>970</v>
       </c>
       <c r="Y10" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB10" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AK10" t="n">
         <v>32</v>
@@ -2988,131 +2988,639 @@
         <v>55</v>
       </c>
       <c r="AM10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-14 05:31:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-14 05:31:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X12" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM12" t="n">
         <v>170</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AN12" t="n">
         <v>46</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AO12" t="n">
         <v>90</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AP12" t="n">
         <v>5.6</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AQ12" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AR12" t="n">
         <v>3.85</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AS12" t="n">
         <v>5.9</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AT12" t="n">
         <v>5</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AU12" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AV12" t="n">
         <v>6.8</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AW12" t="n">
         <v>10</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AX12" t="n">
         <v>6.6</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="AY12" t="n">
         <v>6</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="AZ12" t="n">
         <v>5.7</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BA12" t="n">
         <v>2.8</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BB12" t="n">
         <v>3.2</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BC12" t="n">
         <v>4</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BD12" t="n">
         <v>2.76</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BE12" t="n">
         <v>3</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BF12" t="n">
         <v>8.6</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BG12" t="n">
         <v>3.7</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BH12" t="n">
         <v>3.45</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BI12" t="n">
         <v>2.36</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
         <v>1.42</v>
       </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
         <v>1.42</v>
       </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO10" t="n">
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
         <v>1.42</v>
       </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
         <v>1.42</v>
       </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
         <v>1.42</v>
       </c>
-      <c r="BT10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU10" t="n">
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
         <v>1.42</v>
       </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
         <v>1.42</v>
       </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
         <v>1.42</v>
       </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
         <v>1.42</v>
       </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-06-14 03:16:20</t>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-14 05:31:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -914,7 +914,7 @@
         <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
         <v>15</v>
@@ -1001,7 +1001,7 @@
         <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC2" t="n">
         <v>30</v>
@@ -1010,10 +1010,10 @@
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG2" t="n">
         <v>10</v>
@@ -1064,7 +1064,7 @@
         <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
         <v>26</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>2.16</v>
       </c>
       <c r="G3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H3" t="n">
         <v>3.25</v>
@@ -1129,13 +1129,13 @@
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.26</v>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
         <v>7.8</v>
@@ -1246,7 +1246,7 @@
         <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
@@ -1258,7 +1258,7 @@
         <v>19.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BD3" t="n">
         <v>24</v>
@@ -1267,7 +1267,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BG3" t="n">
         <v>18</v>
@@ -1315,7 +1315,7 @@
         <v>6</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BW3" t="n">
         <v>9.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1640,7 +1640,7 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
         <v>1.25</v>
@@ -1649,7 +1649,7 @@
         <v>1.12</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
         <v>1.12</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,19 +1897,19 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.06</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
         <v>1.06</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
         <v>1.05</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="O7" t="n">
         <v>1.02</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
         <v>1.02</v>
@@ -2166,7 +2166,7 @@
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>4.6</v>
@@ -2402,7 +2402,7 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
         <v>3.65</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>3.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
         <v>1.13</v>
@@ -2668,19 +2668,19 @@
         <v>1.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R9" t="n">
         <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
         <v>1.22</v>
@@ -2689,10 +2689,10 @@
         <v>1.81</v>
       </c>
       <c r="X9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
         <v>42</v>
@@ -2701,7 +2701,7 @@
         <v>180</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC9" t="n">
         <v>9</v>
@@ -2749,10 +2749,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT9" t="n">
         <v>4.8</v>
@@ -2761,52 +2761,52 @@
         <v>5.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>15.5</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.6</v>
+        <v>3.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>20</v>
+        <v>4.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BD9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.2</v>
       </c>
-      <c r="BE9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BG9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ9" t="n">
         <v>13</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2821,16 +2821,16 @@
         <v>3.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR9" t="n">
         <v>48</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT9" t="n">
         <v>8.4</v>
@@ -2839,26 +2839,26 @@
         <v>4.7</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>55</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -3000,13 +3000,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AR10" t="n">
         <v>4.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
         <v>6.6</v>
@@ -3015,40 +3015,40 @@
         <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AY10" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD10" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC10" t="n">
+      <c r="BE10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF10" t="n">
         <v>4.3</v>
       </c>
-      <c r="BD10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH10" t="n">
         <v>3.2</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="G11" t="n">
         <v>2.42</v>
@@ -3152,28 +3152,28 @@
         <v>3.85</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1.09</v>
+        <v>2.46</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
         <v>2.42</v>
       </c>
       <c r="O11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q11" t="n">
         <v>2.38</v>
@@ -3191,7 +3191,7 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
         <v>1.7</v>
@@ -3215,7 +3215,7 @@
         <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AE11" t="n">
         <v>100</v>
@@ -3227,7 +3227,7 @@
         <v>15.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
@@ -3245,64 +3245,64 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AR11" t="n">
         <v>19.5</v>
       </c>
       <c r="AS11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>2.64</v>
       </c>
-      <c r="AT11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BA11" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.64</v>
+        <v>15</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G12" t="n">
         <v>2.52</v>
@@ -3406,7 +3406,7 @@
         <v>3.35</v>
       </c>
       <c r="I12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
         <v>3.1</v>
@@ -3427,7 +3427,7 @@
         <v>1.45</v>
       </c>
       <c r="P12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
         <v>2.34</v>
@@ -3436,19 +3436,19 @@
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T12" t="n">
         <v>1.96</v>
       </c>
       <c r="U12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V12" t="n">
         <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X12" t="n">
         <v>970</v>
@@ -3481,7 +3481,7 @@
         <v>17.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI12" t="n">
         <v>100</v>
@@ -3505,16 +3505,16 @@
         <v>90</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR12" t="n">
         <v>3.85</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT12" t="n">
         <v>5</v>
@@ -3523,40 +3523,40 @@
         <v>6.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW12" t="n">
         <v>10</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BC12" t="n">
         <v>4</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BH12" t="n">
         <v>3.45</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-14 05:31:26</t>
+          <t>2026-06-14 07:45:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,7 +872,7 @@
         <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
         <v>2.32</v>
@@ -1126,10 +1126,10 @@
         <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1138,7 +1138,7 @@
         <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
         <v>2.14</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,66 +1351,66 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sacachispas</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CA Argentino de Rosario</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
         <v>1.02</v>
       </c>
-      <c r="G4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1.02</v>
       </c>
-      <c r="I4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.12</v>
-      </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1530,72 +1530,72 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,33 +1605,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Sacachispas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>CA Argentino de Rosario</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1640,25 +1640,25 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.12</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.24</v>
-      </c>
       <c r="S5" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
@@ -1864,55 +1864,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kari</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.02</v>
       </c>
-      <c r="G6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
         <v>1.02</v>
       </c>
-      <c r="I6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,28 +2118,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,19 +2151,19 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
         <v>1.05</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,60 +2367,60 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="G8" t="n">
-        <v>1.76</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>1.77</v>
       </c>
       <c r="O8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.24</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.4</v>
-      </c>
       <c r="S8" t="n">
-        <v>2.68</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
@@ -2621,244 +2621,244 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>Maranhao</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="G9" t="n">
-        <v>2.22</v>
+        <v>1.76</v>
       </c>
       <c r="H9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
         <v>4.5</v>
       </c>
-      <c r="I9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.1</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>2.38</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.76</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>5.9</v>
+        <v>2.68</v>
       </c>
       <c r="T9" t="n">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.1</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>2.76</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="U10" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AC10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AR10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AV10" t="n">
         <v>4</v>
       </c>
       <c r="AW10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN10" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD10" t="n">
+      <c r="BO10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU10" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.41</v>
+        <v>9.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.4</v>
+        <v>9</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,244 +3129,244 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="G11" t="n">
         <v>2.42</v>
       </c>
       <c r="H11" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="I11" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
         <v>1.7</v>
       </c>
       <c r="X11" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Y11" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
         <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.46</v>
+        <v>3.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>19.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.88</v>
+        <v>4.9</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.22</v>
+        <v>6.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.22</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.46</v>
+        <v>3.9</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.42</v>
+        <v>8.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.64</v>
+        <v>4.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.68</v>
+        <v>4.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.68</v>
+        <v>4.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.76</v>
+        <v>4.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="BF11" t="n">
-        <v>15</v>
+        <v>4.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-14 07:45:58</t>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,206 +3421,460 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="O12" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="X12" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="Z12" t="n">
         <v>34</v>
       </c>
       <c r="AA12" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AB12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF12" t="n">
         <v>12</v>
       </c>
-      <c r="AC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>21</v>
-      </c>
       <c r="AG12" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
         <v>950</v>
       </c>
       <c r="AI12" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ12" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL12" t="n">
         <v>55</v>
       </c>
       <c r="AM12" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-14 09:59:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X13" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM13" t="n">
         <v>170</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AN13" t="n">
         <v>46</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AO13" t="n">
         <v>90</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AP13" t="n">
         <v>5.7</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AQ13" t="n">
         <v>5.9</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AR13" t="n">
         <v>3.85</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AS13" t="n">
         <v>5.8</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AT13" t="n">
         <v>5</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AU13" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AV13" t="n">
         <v>7</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AW13" t="n">
         <v>10</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AX13" t="n">
         <v>6.8</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="AY13" t="n">
         <v>6.2</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="AZ13" t="n">
         <v>5.6</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BA13" t="n">
         <v>2.76</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BB13" t="n">
         <v>3.15</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BC13" t="n">
         <v>4</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BD13" t="n">
         <v>2.7</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BE13" t="n">
         <v>2.96</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BF13" t="n">
         <v>9</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BG13" t="n">
         <v>3.65</v>
       </c>
-      <c r="BH12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>2026-06-14 07:45:58</t>
+      <c r="BH13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-14 09:59:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,7 +863,7 @@
         <v>3.75</v>
       </c>
       <c r="H2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I2" t="n">
         <v>2.2</v>
@@ -872,7 +872,7 @@
         <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -914,7 +914,7 @@
         <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
         <v>15</v>
@@ -1001,7 +1001,7 @@
         <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC2" t="n">
         <v>30</v>
@@ -1010,10 +1010,10 @@
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BG2" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
@@ -1129,13 +1129,13 @@
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.25</v>
@@ -1147,7 +1147,7 @@
         <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
         <v>2.88</v>
@@ -1219,7 +1219,7 @@
         <v>42</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>13.5</v>
@@ -1231,7 +1231,7 @@
         <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU3" t="n">
         <v>7.8</v>
@@ -1246,7 +1246,7 @@
         <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
@@ -1258,7 +1258,7 @@
         <v>19.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD3" t="n">
         <v>24</v>
@@ -1267,7 +1267,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BG3" t="n">
         <v>18</v>
@@ -1300,7 +1300,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR3" t="n">
         <v>38</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
@@ -1365,163 +1365,163 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M4" t="n">
         <v>1.02</v>
       </c>
-      <c r="K4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N4" t="n">
-        <v>1.05</v>
+        <v>7.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="S4" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP4" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BB4" t="n">
         <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE4" t="n">
         <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,66 +1859,66 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>General Lamadrid</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J6" t="n">
         <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S6" t="n">
         <v>1.02</v>
       </c>
-      <c r="N6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.12</v>
-      </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2038,65 +2038,65 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
@@ -2118,12 +2118,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kari</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2139,34 +2139,34 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
         <v>1.02</v>
       </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,19 +2405,19 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
         <v>1.05</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,60 +2621,60 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.65</v>
+        <v>1.02</v>
       </c>
       <c r="G9" t="n">
-        <v>1.76</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.24</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.4</v>
-      </c>
       <c r="S9" t="n">
-        <v>2.68</v>
+        <v>1.05</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2683,10 +2683,10 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
@@ -2875,244 +2875,244 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>Maranhao</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="G10" t="n">
-        <v>2.22</v>
+        <v>1.76</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.76</v>
+        <v>1.73</v>
       </c>
       <c r="R10" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>5.9</v>
+        <v>2.68</v>
       </c>
       <c r="T10" t="n">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="G11" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="H11" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="J11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.1</v>
       </c>
-      <c r="K11" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>2.34</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>2.76</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="V11" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="X11" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AA11" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI11" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AM11" t="n">
-        <v>150</v>
+        <v>310</v>
       </c>
       <c r="AN11" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AO11" t="n">
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS11" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS11" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AT11" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU11" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY11" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD11" t="n">
         <v>4.2</v>
       </c>
-      <c r="BA11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD11" t="n">
+      <c r="BE11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN11" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>12</v>
-      </c>
       <c r="BO11" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.41</v>
+        <v>9.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.4</v>
+        <v>9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,244 +3383,244 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.7</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.85</v>
-      </c>
       <c r="X12" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Y12" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
         <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
         <v>950</v>
       </c>
       <c r="AI12" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AK12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
         <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="AN12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO12" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="AP12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY12" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-14 09:59:38</t>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>
@@ -3642,239 +3642,493 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.34</v>
+        <v>2.02</v>
       </c>
       <c r="G13" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="P13" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W13" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y13" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="Z13" t="n">
         <v>34</v>
       </c>
       <c r="AA13" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AB13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="n">
         <v>12</v>
       </c>
-      <c r="AC13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>21</v>
-      </c>
       <c r="AG13" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH13" t="n">
         <v>950</v>
       </c>
       <c r="AI13" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ13" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
         <v>55</v>
       </c>
       <c r="AM13" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-14 12:11:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X14" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM14" t="n">
         <v>170</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AN14" t="n">
         <v>46</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AO14" t="n">
         <v>90</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AP14" t="n">
         <v>5.7</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AQ14" t="n">
         <v>5.9</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AR14" t="n">
         <v>3.85</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AS14" t="n">
         <v>5.8</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AT14" t="n">
         <v>5</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AU14" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AV14" t="n">
         <v>7</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AW14" t="n">
         <v>10</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AX14" t="n">
         <v>6.8</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="AY14" t="n">
         <v>6.2</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="AZ14" t="n">
         <v>5.6</v>
       </c>
-      <c r="BA13" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BB13" t="n">
+      <c r="BA14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BB14" t="n">
         <v>3.15</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BC14" t="n">
         <v>4</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BD14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI14" t="n">
         <v>2.7</v>
       </c>
-      <c r="BE13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
         <v>6.4</v>
       </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
         <v>2.22</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BN14" t="n">
         <v>5.1</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BO14" t="n">
         <v>3.95</v>
       </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>3.3</v>
       </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
         <v>2.86</v>
       </c>
-      <c r="BT13" t="n">
+      <c r="BT14" t="n">
         <v>6.6</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="BU14" t="n">
         <v>4.9</v>
       </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
         <v>2.78</v>
       </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
         <v>2.86</v>
       </c>
-      <c r="BZ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA13" t="n">
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
         <v>2.66</v>
       </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>2026-06-14 09:59:38</t>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-14 12:11:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -881,67 +881,67 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="V2" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="W2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
         <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AB2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF2" t="n">
         <v>36</v>
       </c>
       <c r="AG2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH2" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
         <v>42</v>
@@ -950,7 +950,7 @@
         <v>85</v>
       </c>
       <c r="AK2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AL2" t="n">
         <v>55</v>
@@ -959,7 +959,7 @@
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO2" t="n">
         <v>15.5</v>
@@ -968,10 +968,10 @@
         <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS2" t="n">
         <v>19.5</v>
@@ -980,10 +980,10 @@
         <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW2" t="n">
         <v>18.5</v>
@@ -995,13 +995,13 @@
         <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
         <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
         <v>30</v>
@@ -1010,13 +1010,13 @@
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.6</v>
+        <v>24</v>
       </c>
       <c r="BG2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH2" t="n">
         <v>3.85</v>
@@ -1034,16 +1034,16 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN2" t="n">
         <v>7</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BP2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ2" t="n">
         <v>9.800000000000001</v>
@@ -1070,17 +1070,17 @@
         <v>26</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>21</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G3" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H3" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="T3" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="U3" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V3" t="n">
         <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="Z3" t="n">
         <v>36</v>
@@ -1177,13 +1177,13 @@
         <v>80</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
         <v>44</v>
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
         <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
         <v>12.5</v>
@@ -1246,28 +1246,28 @@
         <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
         <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BG3" t="n">
         <v>18</v>
@@ -1282,19 +1282,19 @@
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
         <v>5.3</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP3" t="n">
         <v>15.5</v>
@@ -1306,10 +1306,10 @@
         <v>38</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU3" t="n">
         <v>6</v>
@@ -1318,23 +1318,23 @@
         <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>21</v>
       </c>
       <c r="CA3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="G4" t="n">
         <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I4" t="n">
         <v>2.4</v>
@@ -1380,7 +1380,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1389,7 +1389,7 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
         <v>1.13</v>
@@ -1413,10 +1413,10 @@
         <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X4" t="n">
         <v>42</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
         <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
         <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
         <v>1.12</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.02</v>
@@ -2668,7 +2668,7 @@
         <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -3146,46 +3146,46 @@
         <v>2.06</v>
       </c>
       <c r="G11" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
         <v>5.4</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="K11" t="n">
         <v>3.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="R11" t="n">
         <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
         <v>1.63</v>
@@ -3194,16 +3194,16 @@
         <v>1.23</v>
       </c>
       <c r="W11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X11" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="n">
         <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA11" t="n">
         <v>180</v>
@@ -3257,10 +3257,10 @@
         <v>8.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT11" t="n">
         <v>4.7</v>
@@ -3272,55 +3272,55 @@
         <v>15.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
         <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB11" t="n">
         <v>20</v>
       </c>
       <c r="BC11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="BJ11" t="n">
         <v>13</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN11" t="n">
         <v>4.7</v>
@@ -3329,19 +3329,19 @@
         <v>3.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU11" t="n">
         <v>4.7</v>
@@ -3350,23 +3350,23 @@
         <v>60</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>60</v>
+      </c>
+      <c r="CA11" t="n">
         <v>9.6</v>
       </c>
-      <c r="BZ11" t="n">
-        <v>55</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>9</v>
-      </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>3.15</v>
@@ -3699,10 +3699,10 @@
         <v>1.71</v>
       </c>
       <c r="V13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X13" t="n">
         <v>9.800000000000001</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
         <v>3.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="M14" t="n">
         <v>1.1</v>
@@ -3962,7 +3962,7 @@
         <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
         <v>34</v>
@@ -3986,7 +3986,7 @@
         <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
         <v>950</v>
@@ -4019,10 +4019,10 @@
         <v>5.9</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AT14" t="n">
         <v>5</v>
@@ -4043,28 +4043,28 @@
         <v>6.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.96</v>
+        <v>2.38</v>
       </c>
       <c r="BF14" t="n">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="BH14" t="n">
         <v>2.94</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-14 12:11:34</t>
+          <t>2026-06-14 14:21:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -863,13 +863,13 @@
         <v>3.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I2" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
@@ -887,10 +887,10 @@
         <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
         <v>1.49</v>
@@ -905,7 +905,7 @@
         <v>2.42</v>
       </c>
       <c r="V2" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="W2" t="n">
         <v>1.37</v>
@@ -914,7 +914,7 @@
         <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
         <v>16</v>
@@ -938,7 +938,7 @@
         <v>36</v>
       </c>
       <c r="AG2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
         <v>15.5</v>
@@ -959,7 +959,7 @@
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AO2" t="n">
         <v>15.5</v>
@@ -968,7 +968,7 @@
         <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
         <v>13.5</v>
@@ -1022,19 +1022,19 @@
         <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ2" t="n">
         <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN2" t="n">
         <v>7</v>
@@ -1046,41 +1046,41 @@
         <v>26</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR2" t="n">
         <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT2" t="n">
         <v>5.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
         <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX2" t="n">
         <v>26</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA2" t="n">
         <v>9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G3" t="n">
         <v>2.26</v>
@@ -1120,7 +1120,7 @@
         <v>3.35</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J3" t="n">
         <v>3.75</v>
@@ -1159,10 +1159,10 @@
         <v>2.38</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
@@ -1195,7 +1195,7 @@
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
         <v>55</v>
@@ -1219,7 +1219,7 @@
         <v>42</v>
       </c>
       <c r="AP3" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>13.5</v>
@@ -1228,7 +1228,7 @@
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>10.5</v>
@@ -1255,16 +1255,16 @@
         <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF3" t="n">
         <v>10</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="G4" t="n">
         <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I4" t="n">
         <v>2.4</v>
@@ -1380,7 +1380,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1389,7 +1389,7 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.13</v>
@@ -1398,13 +1398,13 @@
         <v>3.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R4" t="n">
         <v>1.84</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T4" t="n">
         <v>1.4</v>
@@ -1413,16 +1413,16 @@
         <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W4" t="n">
         <v>1.45</v>
       </c>
       <c r="X4" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="Y4" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="Z4" t="n">
         <v>26</v>
@@ -1431,7 +1431,7 @@
         <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AC4" t="n">
         <v>12.5</v>
@@ -1470,10 +1470,10 @@
         <v>16.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ4" t="n">
         <v>15.5</v>
@@ -1482,7 +1482,7 @@
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
         <v>18</v>
@@ -1497,7 +1497,7 @@
         <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY4" t="n">
         <v>10.5</v>
@@ -1509,7 +1509,7 @@
         <v>18</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
@@ -1518,77 +1518,77 @@
         <v>21</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF4" t="n">
         <v>10.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.25</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1903,28 +1903,28 @@
         <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.02</v>
       </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2038,65 +2038,65 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O7" t="n">
         <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q7" t="n">
         <v>1.12</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,7 +2405,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
         <v>1.06</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
         <v>1.73</v>
@@ -2937,7 +2937,7 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W10" t="n">
         <v>2.3</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>5.4</v>
       </c>
       <c r="J11" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K11" t="n">
         <v>3.1</v>
@@ -3308,10 +3308,10 @@
         <v>2.62</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="BJ11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK11" t="n">
         <v>6</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN11" t="n">
         <v>4.7</v>
@@ -3332,13 +3332,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR11" t="n">
         <v>50</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT11" t="n">
         <v>8.199999999999999</v>
@@ -3350,23 +3350,23 @@
         <v>60</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ11" t="n">
         <v>60</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>3.15</v>
@@ -3672,7 +3672,7 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
         <v>2.78</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G14" t="n">
         <v>2.54</v>
@@ -3920,7 +3920,7 @@
         <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
         <v>1.51</v>
@@ -3953,13 +3953,13 @@
         <v>1.9</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
         <v>1.65</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
@@ -4013,58 +4013,58 @@
         <v>90</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AS14" t="n">
         <v>4.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU14" t="n">
         <v>6.2</v>
       </c>
       <c r="AV14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX14" t="n">
         <v>7</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>6.8</v>
       </c>
       <c r="AY14" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BA14" t="n">
         <v>2.36</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BD14" t="n">
         <v>2.32</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>17.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="BH14" t="n">
         <v>2.94</v>
@@ -4082,7 +4082,7 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>2.22</v>
+        <v>10</v>
       </c>
       <c r="BN14" t="n">
         <v>5.1</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-14 14:21:20</t>
+          <t>2026-06-14 16:30:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,7 +863,7 @@
         <v>3.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I2" t="n">
         <v>2.26</v>
@@ -872,7 +872,7 @@
         <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -893,16 +893,16 @@
         <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V2" t="n">
         <v>1.79</v>
@@ -956,7 +956,7 @@
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AN2" t="n">
         <v>30</v>
@@ -1001,7 +1001,7 @@
         <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
         <v>30</v>
@@ -1022,7 +1022,7 @@
         <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ2" t="n">
         <v>9</v>
@@ -1058,7 +1058,7 @@
         <v>5.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV2" t="n">
         <v>15</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G3" t="n">
         <v>2.26</v>
@@ -1120,13 +1120,13 @@
         <v>3.35</v>
       </c>
       <c r="I3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.35</v>
@@ -1144,13 +1144,13 @@
         <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R3" t="n">
         <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T3" t="n">
         <v>1.63</v>
@@ -1162,7 +1162,7 @@
         <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
@@ -1174,7 +1174,7 @@
         <v>36</v>
       </c>
       <c r="AA3" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AB3" t="n">
         <v>12.5</v>
@@ -1207,10 +1207,10 @@
         <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AM3" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AN3" t="n">
         <v>20</v>
@@ -1219,7 +1219,7 @@
         <v>42</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
         <v>13.5</v>
@@ -1228,7 +1228,7 @@
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AT3" t="n">
         <v>10.5</v>
@@ -1261,10 +1261,10 @@
         <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
         <v>10</v>
@@ -1279,7 +1279,7 @@
         <v>3.45</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK3" t="n">
         <v>7.8</v>
@@ -1288,16 +1288,16 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO3" t="n">
         <v>4.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ3" t="n">
         <v>9.199999999999999</v>
@@ -1306,7 +1306,7 @@
         <v>38</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
@@ -1318,23 +1318,23 @@
         <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX3" t="n">
         <v>48</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>21</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1395,7 +1395,7 @@
         <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
         <v>1.41</v>
@@ -1413,22 +1413,22 @@
         <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="W4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
       </c>
       <c r="Y4" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="Z4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="n">
         <v>950</v>
@@ -1437,13 +1437,13 @@
         <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF4" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AG4" t="n">
         <v>16.5</v>
@@ -1452,28 +1452,28 @@
         <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AJ4" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL4" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AM4" t="n">
-        <v>50</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
         <v>16.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AQ4" t="n">
         <v>15.5</v>
@@ -1482,7 +1482,7 @@
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AT4" t="n">
         <v>18</v>
@@ -1497,10 +1497,10 @@
         <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>10.5</v>
@@ -1509,7 +1509,7 @@
         <v>18</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
@@ -1518,13 +1518,13 @@
         <v>21</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="BH4" t="n">
         <v>5.1</v>
@@ -1536,34 +1536,34 @@
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BN4" t="n">
         <v>7</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BU4" t="n">
         <v>4.7</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
         <v>7.2</v>
       </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sacachispas</t>
+          <t>CA Fenix</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CA Argentino de Rosario</t>
+          <t>Leones de Rosario</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1631,10 +1631,10 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,28 +1643,28 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q5" t="n">
         <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
         <v>1.02</v>
@@ -1727,122 +1727,122 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
         <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
@@ -1864,31 +1864,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sportivo Barracas</t>
+          <t>Sacachispas</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>General Lamadrid</t>
+          <t>CA Argentino de Rosario</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -1909,7 +1909,7 @@
         <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S6" t="n">
         <v>1.05</v>
@@ -1921,13 +1921,13 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -1936,7 +1936,7 @@
         <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
         <v>1000</v>
@@ -1963,7 +1963,7 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
         <v>1000</v>
@@ -1981,58 +1981,58 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,60 +2113,60 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Sportivo Barracas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>General Lamadrid</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.96</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.12</v>
       </c>
-      <c r="P7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.24</v>
-      </c>
       <c r="S7" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2175,13 +2175,13 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
         <v>1000</v>
@@ -2196,7 +2196,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -2235,58 +2235,58 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
@@ -2372,246 +2372,246 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kari</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1.69</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1.09</v>
+        <v>4.8</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.06</v>
+        <v>1.39</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>1.96</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>2.58</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.02</v>
+        <v>1.71</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.88</v>
       </c>
       <c r="H9" t="n">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>11</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P9" t="n">
         <v>4.3</v>
       </c>
-      <c r="K9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="S9" t="n">
-        <v>1.05</v>
+        <v>1.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.76</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="I10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>13</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X10" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>17</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BW10" t="n">
         <v>6.2</v>
       </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,244 +3129,244 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Sportivo Belgrano</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>Def Belgrano VR</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="G11" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="I11" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="O11" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="S11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.1</v>
+        <v>1.05</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.4</v>
+        <v>1.05</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Maranhao</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.14</v>
+        <v>1.63</v>
       </c>
       <c r="G12" t="n">
-        <v>2.42</v>
+        <v>1.76</v>
       </c>
       <c r="H12" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9</v>
+        <v>2.68</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="V12" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="X12" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE12" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AF12" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AH12" t="n">
         <v>950</v>
       </c>
       <c r="AI12" t="n">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="AJ12" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AO12" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.8</v>
+        <v>1.26</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.3</v>
+        <v>1.26</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.9</v>
+        <v>1.27</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>1.21</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>1.23</v>
       </c>
       <c r="AV12" t="n">
-        <v>4</v>
+        <v>1.26</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.7</v>
+        <v>1.27</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.9</v>
+        <v>1.23</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.6</v>
+        <v>1.23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.2</v>
+        <v>1.25</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.8</v>
+        <v>1.27</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.5</v>
+        <v>1.26</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>1.26</v>
       </c>
       <c r="BE12" t="n">
-        <v>5</v>
+        <v>1.27</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.3</v>
+        <v>1.24</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.8</v>
+        <v>1.55</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="H13" t="n">
         <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="S13" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="U13" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W13" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="X13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>50</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Y13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-14 16:30:24</t>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,111 +3891,111 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="G14" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="H14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I14" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
         <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Z14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA14" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB14" t="n">
-        <v>12</v>
+        <v>950</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AH14" t="n">
         <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AK14" t="n">
         <v>32</v>
@@ -4004,88 +4004,88 @@
         <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN14" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AO14" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU14" t="n">
         <v>6</v>
       </c>
-      <c r="AR14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS14" t="n">
+      <c r="AV14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF14" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BG14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
         <v>5.1</v>
       </c>
-      <c r="AU14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="BO14" t="n">
         <v>3.95</v>
@@ -4094,41 +4094,549 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-14 18:38:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-14 18:38:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X16" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
         <v>3.3</v>
       </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
         <v>2.86</v>
       </c>
-      <c r="BT14" t="n">
+      <c r="BT16" t="n">
         <v>6.6</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="BU16" t="n">
         <v>4.9</v>
       </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
         <v>2.78</v>
       </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
         <v>2.86</v>
       </c>
-      <c r="BZ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA14" t="n">
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
         <v>2.66</v>
       </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>2026-06-14 16:30:24</t>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-14 18:38:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -863,7 +863,7 @@
         <v>3.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I2" t="n">
         <v>2.26</v>
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF2" t="n">
         <v>24</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>2.16</v>
       </c>
       <c r="G3" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
         <v>3.7</v>
@@ -1138,31 +1138,31 @@
         <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="T3" t="n">
         <v>1.63</v>
       </c>
       <c r="U3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
         <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
@@ -1195,7 +1195,7 @@
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
         <v>55</v>
@@ -1213,7 +1213,7 @@
         <v>320</v>
       </c>
       <c r="AN3" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AO3" t="n">
         <v>42</v>
@@ -1255,13 +1255,13 @@
         <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
         <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE3" t="n">
         <v>28</v>
@@ -1273,25 +1273,25 @@
         <v>18</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI3" t="n">
         <v>3.45</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO3" t="n">
         <v>4.6</v>
@@ -1306,7 +1306,7 @@
         <v>38</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
@@ -1318,23 +1318,23 @@
         <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX3" t="n">
         <v>48</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
         <v>3.4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I4" t="n">
         <v>2.26</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1407,7 +1407,7 @@
         <v>2.02</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U4" t="n">
         <v>3.05</v>
@@ -1428,13 +1428,13 @@
         <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
         <v>950</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
         <v>13</v>
@@ -1449,13 +1449,13 @@
         <v>16.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI4" t="n">
         <v>26</v>
       </c>
       <c r="AJ4" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
         <v>75</v>
@@ -1473,7 +1473,7 @@
         <v>8.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
         <v>15.5</v>
@@ -1482,10 +1482,10 @@
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU4" t="n">
         <v>8.4</v>
@@ -1497,7 +1497,7 @@
         <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
         <v>11.5</v>
@@ -1509,7 +1509,7 @@
         <v>18</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
@@ -1518,13 +1518,13 @@
         <v>21</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="n">
         <v>5.1</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1643,28 +1643,28 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
         <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.02</v>
@@ -1784,65 +1784,65 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
         <v>1.01</v>
@@ -1927,109 +1927,109 @@
         <v>1.46</v>
       </c>
       <c r="X6" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y6" t="n">
         <v>950</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
         <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
         <v>3.85</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="BG6" t="n">
         <v>1.55</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G7" t="n">
         <v>44</v>
       </c>
       <c r="H7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I7" t="n">
         <v>44</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
         <v>1.01</v>
@@ -2184,103 +2184,103 @@
         <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AQ7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AU7" t="n">
         <v>1.11</v>
       </c>
-      <c r="AR7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AV7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BF7" t="n">
         <v>1.55</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
         <v>4.8</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L8" t="n">
         <v>1.2</v>
@@ -2405,7 +2405,7 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.13</v>
@@ -2414,7 +2414,7 @@
         <v>3.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R8" t="n">
         <v>1.86</v>
@@ -2423,16 +2423,16 @@
         <v>1.96</v>
       </c>
       <c r="T8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U8" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="X8" t="n">
         <v>40</v>
@@ -2450,7 +2450,7 @@
         <v>17</v>
       </c>
       <c r="AC8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
         <v>23</v>
@@ -2459,7 +2459,7 @@
         <v>120</v>
       </c>
       <c r="AF8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
@@ -2471,7 +2471,7 @@
         <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK8" t="n">
         <v>15.5</v>
@@ -2483,22 +2483,22 @@
         <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AO8" t="n">
         <v>40</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ8" t="n">
         <v>14.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>14</v>
@@ -2510,7 +2510,7 @@
         <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX8" t="n">
         <v>12.5</v>
@@ -2522,7 +2522,7 @@
         <v>14.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB8" t="n">
         <v>15</v>
@@ -2534,19 +2534,19 @@
         <v>19.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH8" t="n">
         <v>5.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.199999999999999</v>
@@ -2558,19 +2558,19 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN8" t="n">
         <v>5.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR8" t="n">
         <v>18</v>
@@ -2579,7 +2579,7 @@
         <v>6.8</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU8" t="n">
         <v>5.2</v>
@@ -2591,7 +2591,7 @@
         <v>8.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY8" t="n">
         <v>8.4</v>
@@ -2600,11 +2600,11 @@
         <v>10.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I9" t="n">
         <v>4.3</v>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.07</v>
@@ -2680,13 +2680,13 @@
         <v>1.33</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="V9" t="n">
         <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X9" t="n">
         <v>80</v>
@@ -2707,7 +2707,7 @@
         <v>17</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>38</v>
@@ -2722,7 +2722,7 @@
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ9" t="n">
         <v>27</v>
@@ -2743,7 +2743,7 @@
         <v>18</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ9" t="n">
         <v>6.4</v>
@@ -2752,19 +2752,19 @@
         <v>6.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX9" t="n">
         <v>16.5</v>
@@ -2779,7 +2779,7 @@
         <v>21</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC9" t="n">
         <v>12</v>
@@ -2788,10 +2788,10 @@
         <v>14</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="BG9" t="n">
         <v>10.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -2964,13 +2964,13 @@
         <v>17.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
         <v>46</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AH10" t="n">
         <v>15</v>
@@ -2985,7 +2985,7 @@
         <v>25</v>
       </c>
       <c r="AL10" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AM10" t="n">
         <v>34</v>
@@ -2997,19 +2997,19 @@
         <v>7.8</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AU10" t="n">
         <v>13</v>
@@ -3021,7 +3021,7 @@
         <v>16.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AY10" t="n">
         <v>12</v>
@@ -3033,7 +3033,7 @@
         <v>15</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BC10" t="n">
         <v>17</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3167,28 +3167,28 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O11" t="n">
         <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="R11" t="n">
         <v>1.12</v>
       </c>
       <c r="S11" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="G12" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="H12" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,34 +3421,34 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
         <v>2.68</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="U12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3466,7 +3466,7 @@
         <v>950</v>
       </c>
       <c r="AC12" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AD12" t="n">
         <v>950</v>
@@ -3505,7 +3505,7 @@
         <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.26</v>
@@ -3517,7 +3517,7 @@
         <v>1.27</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AU12" t="n">
         <v>1.23</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>2.24</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
         <v>5.4</v>
@@ -3759,22 +3759,22 @@
         <v>220</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>8.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS13" t="n">
         <v>4.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV13" t="n">
         <v>15.5</v>
@@ -3798,7 +3798,7 @@
         <v>20</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BD13" t="n">
         <v>4.3</v>
@@ -3807,7 +3807,7 @@
         <v>4.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG13" t="n">
         <v>4.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -3959,10 +3959,10 @@
         <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
         <v>32</v>
@@ -3971,22 +3971,22 @@
         <v>90</v>
       </c>
       <c r="AB14" t="n">
-        <v>950</v>
+        <v>9.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
         <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
         <v>950</v>
@@ -4007,7 +4007,7 @@
         <v>150</v>
       </c>
       <c r="AN14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
         <v>70</v>
@@ -4016,55 +4016,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA14" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BB14" t="n">
         <v>6</v>
       </c>
-      <c r="AV14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BC14" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH14" t="n">
         <v>3.2</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G15" t="n">
         <v>2.02</v>
@@ -4171,7 +4171,7 @@
         <v>5.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
         <v>3.45</v>
@@ -4180,7 +4180,7 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N15" t="n">
         <v>2.82</v>
@@ -4201,10 +4201,10 @@
         <v>4.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="V15" t="n">
         <v>1.22</v>
@@ -4225,7 +4225,7 @@
         <v>150</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC15" t="n">
         <v>7.6</v>
@@ -4240,7 +4240,7 @@
         <v>11</v>
       </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
         <v>950</v>
@@ -4249,16 +4249,16 @@
         <v>110</v>
       </c>
       <c r="AJ15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
         <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="n">
         <v>22</v>
@@ -4273,10 +4273,10 @@
         <v>12.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
         <v>6</v>
@@ -4285,10 +4285,10 @@
         <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX15" t="n">
         <v>9.6</v>
@@ -4297,28 +4297,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
         <v>21</v>
       </c>
       <c r="BC15" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>2.36</v>
       </c>
       <c r="G16" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
         <v>3.75</v>
@@ -4431,16 +4431,16 @@
         <v>3.35</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
         <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="P16" t="n">
         <v>1.65</v>
@@ -4449,7 +4449,7 @@
         <v>2.34</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
         <v>4.6</v>
@@ -4464,13 +4464,13 @@
         <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X16" t="n">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z16" t="n">
         <v>34</v>
@@ -4494,7 +4494,7 @@
         <v>15</v>
       </c>
       <c r="AG16" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
         <v>950</v>
@@ -4521,28 +4521,28 @@
         <v>75</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX16" t="n">
         <v>6.8</v>
@@ -4551,28 +4551,28 @@
         <v>6.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="BB16" t="n">
-        <v>25</v>
+        <v>2.52</v>
       </c>
       <c r="BC16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BF16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BD16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>9</v>
-      </c>
       <c r="BG16" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BH16" t="n">
         <v>2.94</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-14 18:38:51</t>
+          <t>2026-06-14 20:46:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -884,19 +884,19 @@
         <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
         <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T2" t="n">
         <v>1.67</v>
@@ -905,10 +905,10 @@
         <v>2.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
         <v>19</v>
@@ -920,10 +920,10 @@
         <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC2" t="n">
         <v>8.6</v>
@@ -935,7 +935,7 @@
         <v>21</v>
       </c>
       <c r="AF2" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AG2" t="n">
         <v>15</v>
@@ -944,7 +944,7 @@
         <v>15.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AJ2" t="n">
         <v>85</v>
@@ -1004,7 +1004,7 @@
         <v>23</v>
       </c>
       <c r="BC2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BD2" t="n">
         <v>34</v>
@@ -1028,16 +1028,16 @@
         <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO2" t="n">
         <v>6</v>
@@ -1046,41 +1046,41 @@
         <v>26</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BR2" t="n">
         <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
         <v>26</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I3" t="n">
         <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.35</v>
@@ -1135,19 +1135,19 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
         <v>2.76</v>
@@ -1159,10 +1159,10 @@
         <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
@@ -1276,22 +1276,22 @@
         <v>3.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ3" t="n">
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO3" t="n">
         <v>4.6</v>
@@ -1306,7 +1306,7 @@
         <v>38</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
@@ -1318,23 +1318,23 @@
         <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX3" t="n">
         <v>48</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>20</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="I4" t="n">
         <v>2.26</v>
@@ -1398,7 +1398,7 @@
         <v>3.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R4" t="n">
         <v>1.84</v>
@@ -1416,7 +1416,7 @@
         <v>1.79</v>
       </c>
       <c r="W4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
         <v>950</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
         <v>1.01</v>
@@ -1658,7 +1658,7 @@
         <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1670,7 +1670,7 @@
         <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1727,58 +1727,58 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
         <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G7" t="n">
         <v>44</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -2390,13 +2390,13 @@
         <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>4.8</v>
       </c>
       <c r="K8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L8" t="n">
         <v>1.2</v>
@@ -2411,25 +2411,25 @@
         <v>1.13</v>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q8" t="n">
         <v>1.38</v>
       </c>
       <c r="R8" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S8" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="T8" t="n">
         <v>1.52</v>
       </c>
       <c r="U8" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
         <v>2.66</v>
@@ -2438,7 +2438,7 @@
         <v>40</v>
       </c>
       <c r="Y8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="n">
         <v>55</v>
@@ -2468,7 +2468,7 @@
         <v>18</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ8" t="n">
         <v>20</v>
@@ -2483,22 +2483,22 @@
         <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO8" t="n">
         <v>40</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8" t="n">
         <v>14.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT8" t="n">
         <v>14</v>
@@ -2510,7 +2510,7 @@
         <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX8" t="n">
         <v>12.5</v>
@@ -2522,7 +2522,7 @@
         <v>14.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB8" t="n">
         <v>15</v>
@@ -2534,31 +2534,31 @@
         <v>19.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
         <v>4.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8" t="n">
         <v>5.1</v>
@@ -2570,10 +2570,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS8" t="n">
         <v>6.8</v>
@@ -2582,29 +2582,29 @@
         <v>10</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV8" t="n">
         <v>36</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA8" t="n">
         <v>5.3</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.72</v>
       </c>
       <c r="G9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H9" t="n">
         <v>3.65</v>
@@ -2686,7 +2686,7 @@
         <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X9" t="n">
         <v>80</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.83</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>2.84</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,16 +3167,16 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.26</v>
+        <v>2.52</v>
       </c>
       <c r="O11" t="n">
         <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.57</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
         <v>1.12</v>
@@ -3191,172 +3191,172 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK11" t="n">
         <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.05</v>
+        <v>2.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.05</v>
+        <v>2.88</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.58</v>
       </c>
       <c r="G12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H12" t="n">
         <v>5.6</v>
@@ -3421,7 +3421,7 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
@@ -3508,13 +3508,13 @@
         <v>1.26</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.26</v>
+        <v>4.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.26</v>
+        <v>4.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.27</v>
+        <v>4.2</v>
       </c>
       <c r="AT12" t="n">
         <v>1.22</v>
@@ -3523,10 +3523,10 @@
         <v>1.23</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.26</v>
+        <v>4.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.27</v>
+        <v>4.2</v>
       </c>
       <c r="AX12" t="n">
         <v>1.23</v>
@@ -3538,7 +3538,7 @@
         <v>1.25</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.27</v>
+        <v>4.2</v>
       </c>
       <c r="BB12" t="n">
         <v>1.26</v>
@@ -3556,7 +3556,7 @@
         <v>1.24</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
         <v>2.24</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>2.88</v>
@@ -3699,7 +3699,7 @@
         <v>1.63</v>
       </c>
       <c r="V13" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
         <v>1.8</v>
@@ -3765,10 +3765,10 @@
         <v>8.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT13" t="n">
         <v>5.2</v>
@@ -3786,7 +3786,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
         <v>20</v>
@@ -3810,7 +3810,7 @@
         <v>4.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH13" t="n">
         <v>2.62</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="H14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I14" t="n">
         <v>4.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.45</v>
@@ -3929,19 +3929,19 @@
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q14" t="n">
         <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
         <v>3.9</v>
@@ -3950,13 +3950,13 @@
         <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
@@ -3971,7 +3971,7 @@
         <v>90</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
         <v>8.6</v>
@@ -3989,7 +3989,7 @@
         <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI14" t="n">
         <v>75</v>
@@ -4004,7 +4004,7 @@
         <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
         <v>26</v>
@@ -4019,10 +4019,10 @@
         <v>9.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT14" t="n">
         <v>6.8</v>
@@ -4034,7 +4034,7 @@
         <v>12.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -4043,28 +4043,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG14" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>6.6</v>
       </c>
       <c r="BH14" t="n">
         <v>3.2</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -4159,25 +4159,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="n">
         <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M15" t="n">
         <v>1.11</v>
@@ -4204,19 +4204,19 @@
         <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z15" t="n">
         <v>38</v>
@@ -4237,7 +4237,7 @@
         <v>90</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG15" t="n">
         <v>11</v>
@@ -4270,10 +4270,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS15" t="n">
         <v>10</v>
@@ -4285,13 +4285,13 @@
         <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX15" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>9.6</v>
       </c>
       <c r="AY15" t="n">
         <v>9.4</v>
@@ -4300,7 +4300,7 @@
         <v>7.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB15" t="n">
         <v>21</v>
@@ -4309,13 +4309,13 @@
         <v>7.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG15" t="n">
         <v>10</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G16" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I16" t="n">
         <v>3.75</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4437,13 +4437,13 @@
         <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>1.45</v>
       </c>
       <c r="P16" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q16" t="n">
         <v>2.34</v>
@@ -4455,13 +4455,13 @@
         <v>4.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
         <v>1.65</v>
@@ -4497,7 +4497,7 @@
         <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI16" t="n">
         <v>100</v>
@@ -4512,7 +4512,7 @@
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN16" t="n">
         <v>46</v>
@@ -4521,16 +4521,16 @@
         <v>75</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ16" t="n">
         <v>9.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT16" t="n">
         <v>6.2</v>
@@ -4539,40 +4539,40 @@
         <v>6.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BA16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.52</v>
+        <v>4.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="BF16" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BH16" t="n">
         <v>2.94</v>
@@ -4584,16 +4584,16 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>10</v>
+        <v>2.18</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO16" t="n">
         <v>3.95</v>
@@ -4602,13 +4602,13 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>2.86</v>
+        <v>3.95</v>
       </c>
       <c r="BT16" t="n">
         <v>6.6</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.78</v>
+        <v>5.3</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.86</v>
+        <v>3.95</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-14 20:46:35</t>
+          <t>2026-06-14 22:53:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -860,19 +860,19 @@
         <v>3.45</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -881,7 +881,7 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.25</v>
@@ -890,7 +890,7 @@
         <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
         <v>1.48</v>
@@ -902,37 +902,37 @@
         <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V2" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="W2" t="n">
         <v>1.38</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y2" t="n">
         <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF2" t="n">
         <v>27</v>
@@ -947,13 +947,13 @@
         <v>32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AK2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
         <v>320</v>
@@ -974,13 +974,13 @@
         <v>13.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
         <v>9.6</v>
@@ -989,34 +989,34 @@
         <v>18.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="BC2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD2" t="n">
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="n">
         <v>3.85</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J3" t="n">
         <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.35</v>
@@ -1153,22 +1153,22 @@
         <v>2.76</v>
       </c>
       <c r="T3" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X3" t="n">
         <v>26</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
         <v>36</v>
@@ -1207,7 +1207,7 @@
         <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
         <v>320</v>
@@ -1219,16 +1219,16 @@
         <v>42</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AT3" t="n">
         <v>10.5</v>
@@ -1240,7 +1240,7 @@
         <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX3" t="n">
         <v>13.5</v>
@@ -1252,25 +1252,25 @@
         <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC3" t="n">
         <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BE3" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BF3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.9</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
         <v>5.2</v>
@@ -1306,19 +1306,19 @@
         <v>38</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BV3" t="n">
         <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3" t="n">
         <v>48</v>
@@ -1330,11 +1330,11 @@
         <v>20</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="I4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>4.3</v>
@@ -1395,31 +1395,31 @@
         <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.42</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.41</v>
-      </c>
       <c r="U4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="V4" t="n">
         <v>1.79</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y4" t="n">
         <v>22</v>
@@ -1431,25 +1431,25 @@
         <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AC4" t="n">
         <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
       </c>
       <c r="AF4" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AG4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI4" t="n">
         <v>26</v>
@@ -1461,7 +1461,7 @@
         <v>75</v>
       </c>
       <c r="AL4" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
@@ -1470,61 +1470,61 @@
         <v>16.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="AY4" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.6</v>
+        <v>25</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="n">
         <v>5.1</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>3.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>2.06</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="J5" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.25</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.03</v>
-      </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -1873,109 +1873,109 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="G6" t="n">
-        <v>44</v>
+        <v>2.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
-        <v>44</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="K6" t="n">
-        <v>44</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S6" t="n">
-        <v>1.05</v>
+        <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>950</v>
+        <v>10</v>
       </c>
       <c r="Z6" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>950</v>
+        <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AF6" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
         <v>500</v>
@@ -1984,119 +1984,119 @@
         <v>3.85</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.09</v>
+        <v>4.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.09</v>
+        <v>6.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.09</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.09</v>
+        <v>3.95</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.09</v>
+        <v>4</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.09</v>
+        <v>5.9</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.09</v>
+        <v>7.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.09</v>
+        <v>5.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.09</v>
+        <v>5.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.09</v>
+        <v>6.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.09</v>
+        <v>7.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.09</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.09</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -2127,64 +2127,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.96</v>
+        <v>2.58</v>
       </c>
       <c r="G7" t="n">
-        <v>44</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2</v>
+        <v>2.96</v>
       </c>
       <c r="I7" t="n">
-        <v>44</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>44</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S7" t="n">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="X7" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y7" t="n">
         <v>970</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>950</v>
       </c>
       <c r="Z7" t="n">
         <v>500</v>
@@ -2193,22 +2193,22 @@
         <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
@@ -2235,122 +2235,122 @@
         <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.06</v>
+        <v>3.55</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.14</v>
+        <v>3.95</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.14</v>
+        <v>2.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.14</v>
+        <v>2.94</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.14</v>
+        <v>3.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.11</v>
+        <v>3.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.14</v>
+        <v>2.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.14</v>
+        <v>3</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.14</v>
+        <v>2.62</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.14</v>
+        <v>3.05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.14</v>
+        <v>2.76</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.14</v>
+        <v>2.96</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.14</v>
+        <v>2.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.14</v>
+        <v>2.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.14</v>
+        <v>2.96</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.14</v>
+        <v>3</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.55</v>
+        <v>2.94</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.55</v>
+        <v>2.96</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
         <v>4.8</v>
@@ -2420,7 +2420,7 @@
         <v>1.89</v>
       </c>
       <c r="S8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="T8" t="n">
         <v>1.52</v>
@@ -2540,25 +2540,25 @@
         <v>4.3</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="n">
         <v>5.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN8" t="n">
         <v>5.1</v>
@@ -2570,41 +2570,41 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT8" t="n">
         <v>10</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX8" t="n">
         <v>36</v>
       </c>
-      <c r="BW8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>34</v>
-      </c>
       <c r="BY8" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>1.72</v>
       </c>
       <c r="G9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
         <v>4.3</v>
@@ -2683,7 +2683,7 @@
         <v>3.45</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
         <v>2.16</v>
@@ -2800,7 +2800,7 @@
         <v>7.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -2907,34 +2907,34 @@
         <v>5.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
         <v>1.06</v>
       </c>
       <c r="P10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R10" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="S10" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="T10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V10" t="n">
         <v>1.62</v>
@@ -2958,7 +2958,7 @@
         <v>48</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AD10" t="n">
         <v>17.5</v>
@@ -2976,7 +2976,7 @@
         <v>15</v>
       </c>
       <c r="AI10" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AJ10" t="n">
         <v>60</v>
@@ -3045,13 +3045,13 @@
         <v>20</v>
       </c>
       <c r="BF10" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI10" t="n">
         <v>4.5</v>
@@ -3060,16 +3060,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BN10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO10" t="n">
         <v>4.5</v>
@@ -3078,19 +3078,19 @@
         <v>16.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV10" t="n">
         <v>16</v>
@@ -3102,17 +3102,17 @@
         <v>16.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BZ10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -3143,220 +3143,220 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="G11" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="H11" t="n">
-        <v>1.09</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
         <v>2.52</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="P11" t="n">
         <v>1.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.12</v>
       </c>
-      <c r="S11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.11</v>
-      </c>
       <c r="W11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
         <v>2.2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>380</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>210</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="G12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H12" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J12" t="n">
         <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,7 +3421,7 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>1.11</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
@@ -3430,7 +3430,7 @@
         <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R12" t="n">
         <v>1.41</v>
@@ -3445,10 +3445,10 @@
         <v>1.98</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -3654,61 +3654,61 @@
         <v>2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H13" t="n">
         <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="K13" t="n">
         <v>3.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N13" t="n">
         <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="R13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S13" t="n">
         <v>6.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V13" t="n">
         <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X13" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z13" t="n">
         <v>42</v>
@@ -3717,10 +3717,10 @@
         <v>180</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
         <v>27</v>
@@ -3750,28 +3750,28 @@
         <v>85</v>
       </c>
       <c r="AM13" t="n">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="AN13" t="n">
         <v>40</v>
       </c>
       <c r="AO13" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AQ13" t="n">
         <v>8.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU13" t="n">
         <v>6.2</v>
@@ -3780,7 +3780,7 @@
         <v>15.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX13" t="n">
         <v>8.199999999999999</v>
@@ -3789,34 +3789,34 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB13" t="n">
         <v>20</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.4</v>
+        <v>22</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BJ13" t="n">
         <v>13.5</v>
@@ -3843,13 +3843,13 @@
         <v>7</v>
       </c>
       <c r="BR13" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
         <v>9</v>
       </c>
       <c r="BT13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU13" t="n">
         <v>4.7</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L14" t="n">
         <v>1.45</v>
@@ -3932,10 +3932,10 @@
         <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q14" t="n">
         <v>2.12</v>
@@ -3947,16 +3947,16 @@
         <v>3.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V14" t="n">
         <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
@@ -3971,7 +3971,7 @@
         <v>90</v>
       </c>
       <c r="AB14" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC14" t="n">
         <v>8.6</v>
@@ -3986,7 +3986,7 @@
         <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
         <v>970</v>
@@ -4019,10 +4019,10 @@
         <v>9.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT14" t="n">
         <v>6.8</v>
@@ -4031,10 +4031,10 @@
         <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>12.5</v>
+        <v>5.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -4043,92 +4043,92 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE14" t="n">
         <v>5.1</v>
       </c>
-      <c r="BA14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF14" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BH14" t="n">
         <v>3.2</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="BN14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H15" t="n">
         <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J15" t="n">
         <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.51</v>
@@ -4192,7 +4192,7 @@
         <v>1.61</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R15" t="n">
         <v>1.22</v>
@@ -4210,7 +4210,7 @@
         <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="X15" t="n">
         <v>9.800000000000001</v>
@@ -4219,7 +4219,7 @@
         <v>16</v>
       </c>
       <c r="Z15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA15" t="n">
         <v>150</v>
@@ -4288,7 +4288,7 @@
         <v>18.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX15" t="n">
         <v>9.800000000000001</v>
@@ -4297,10 +4297,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
         <v>21</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>
@@ -4413,37 +4413,37 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G16" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I16" t="n">
         <v>3.75</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O16" t="n">
         <v>1.45</v>
       </c>
       <c r="P16" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
         <v>2.34</v>
@@ -4455,7 +4455,7 @@
         <v>4.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U16" t="n">
         <v>1.94</v>
@@ -4470,7 +4470,7 @@
         <v>15.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z16" t="n">
         <v>34</v>
@@ -4491,7 +4491,7 @@
         <v>50</v>
       </c>
       <c r="AF16" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AG16" t="n">
         <v>970</v>
@@ -4521,58 +4521,58 @@
         <v>75</v>
       </c>
       <c r="AP16" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>9.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT16" t="n">
         <v>6.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX16" t="n">
         <v>12.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="BF16" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="BH16" t="n">
         <v>2.94</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.18</v>
+        <v>9.6</v>
       </c>
       <c r="BN16" t="n">
         <v>5.2</v>
@@ -4626,7 +4626,7 @@
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-14 22:53:46</t>
+          <t>2026-06-15 01:00:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -860,43 +860,43 @@
         <v>3.45</v>
       </c>
       <c r="G2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>3.65</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>1.67</v>
@@ -905,28 +905,28 @@
         <v>2.42</v>
       </c>
       <c r="V2" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W2" t="n">
         <v>1.38</v>
       </c>
       <c r="X2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>11.5</v>
@@ -935,10 +935,10 @@
         <v>22</v>
       </c>
       <c r="AF2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
         <v>15.5</v>
@@ -950,91 +950,91 @@
         <v>65</v>
       </c>
       <c r="AK2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
         <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>320</v>
+        <v>75</v>
       </c>
       <c r="AN2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO2" t="n">
         <v>15.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ2" t="n">
         <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BB2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BC2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BD2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="BF2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG2" t="n">
         <v>12.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ2" t="n">
         <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
@@ -1043,19 +1043,19 @@
         <v>6</v>
       </c>
       <c r="BP2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BS2" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU2" t="n">
         <v>4.7</v>
@@ -1064,23 +1064,23 @@
         <v>15.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
         <v>2.22</v>
       </c>
       <c r="H3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I3" t="n">
         <v>3.6</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.75</v>
       </c>
       <c r="J3" t="n">
         <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="T3" t="n">
         <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="X3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z3" t="n">
         <v>36</v>
@@ -1183,19 +1183,19 @@
         <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG3" t="n">
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
         <v>55</v>
@@ -1207,7 +1207,7 @@
         <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AM3" t="n">
         <v>320</v>
@@ -1216,10 +1216,10 @@
         <v>13</v>
       </c>
       <c r="AO3" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AQ3" t="n">
         <v>14.5</v>
@@ -1243,7 +1243,7 @@
         <v>26</v>
       </c>
       <c r="AX3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY3" t="n">
         <v>9.6</v>
@@ -1258,22 +1258,22 @@
         <v>13.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG3" t="n">
         <v>18.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI3" t="n">
         <v>3.5</v>
@@ -1282,16 +1282,16 @@
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO3" t="n">
         <v>4.6</v>
@@ -1303,38 +1303,38 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BR3" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BV3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3" t="n">
         <v>48</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>20</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="I4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R4" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="S4" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
         <v>1.42</v>
       </c>
       <c r="U4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="W4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X4" t="n">
         <v>500</v>
@@ -1425,34 +1425,34 @@
         <v>22</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
         <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AC4" t="n">
         <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AF4" t="n">
         <v>36</v>
       </c>
       <c r="AG4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AJ4" t="n">
         <v>500</v>
@@ -1467,67 +1467,67 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>16.5</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AP4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ4" t="n">
         <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW4" t="n">
         <v>16.5</v>
       </c>
-      <c r="AU4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>16</v>
-      </c>
       <c r="AX4" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AY4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>11.5</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>12</v>
-      </c>
       <c r="BA4" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="BC4" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>19</v>
       </c>
       <c r="BE4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BF4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI4" t="n">
         <v>4.5</v>
@@ -1536,31 +1536,31 @@
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.5</v>
+        <v>2.96</v>
       </c>
       <c r="BN4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
         <v>9.4</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>10</v>
       </c>
       <c r="BT4" t="n">
         <v>5.7</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -1619,61 +1619,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.7</v>
+        <v>2.14</v>
       </c>
       <c r="G5" t="n">
-        <v>5.2</v>
+        <v>44</v>
       </c>
       <c r="H5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I5" t="n">
+        <v>44</v>
+      </c>
+      <c r="J5" t="n">
         <v>2.06</v>
       </c>
-      <c r="I5" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.7</v>
-      </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>44</v>
       </c>
       <c r="L5" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="S5" t="n">
         <v>5.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="U5" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1727,122 +1727,122 @@
         <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.45</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.86</v>
+        <v>1.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.95</v>
+        <v>1.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.86</v>
+        <v>1.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.82</v>
+        <v>1.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.65</v>
+        <v>1.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.15</v>
+        <v>1.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.68</v>
+        <v>1.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.58</v>
+        <v>1.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.58</v>
+        <v>1.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.58</v>
+        <v>1.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.76</v>
+        <v>1.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.46</v>
+        <v>1.55</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
         <v>4.7</v>
       </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.23</v>
-      </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.27</v>
+        <v>4.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.28</v>
+        <v>4.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>2.26</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H6" t="n">
         <v>3.4</v>
@@ -1885,22 +1885,22 @@
         <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="K6" t="n">
         <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="M6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N6" t="n">
         <v>2.14</v>
       </c>
       <c r="O6" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="P6" t="n">
         <v>1.38</v>
@@ -1909,22 +1909,22 @@
         <v>2.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
         <v>7.2</v>
@@ -1945,13 +1945,13 @@
         <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>200</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG6" t="n">
         <v>14</v>
@@ -1963,10 +1963,10 @@
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL6" t="n">
         <v>230</v>
@@ -1975,7 +1975,7 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO6" t="n">
         <v>500</v>
@@ -1984,119 +1984,119 @@
         <v>3.85</v>
       </c>
       <c r="AQ6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
         <v>4.5</v>
       </c>
-      <c r="AR6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
         <v>6.6</v>
       </c>
-      <c r="BA6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB6" t="n">
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
         <v>6.8</v>
       </c>
-      <c r="BD6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>25</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>8.4</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -2127,61 +2127,61 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>8.6</v>
       </c>
       <c r="H7" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="M7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="P7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Q7" t="n">
         <v>2.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="X7" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
@@ -2235,76 +2235,76 @@
         <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.55</v>
+        <v>2.12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.95</v>
+        <v>2.02</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.94</v>
+        <v>2.48</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.75</v>
+        <v>1.99</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.6</v>
+        <v>1.98</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="AW7" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.05</v>
+        <v>2.22</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.76</v>
+        <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.96</v>
+        <v>2.48</v>
       </c>
       <c r="BE7" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.94</v>
+        <v>5.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.96</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="n">
         <v>2.58</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.91</v>
+        <v>1.38</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
@@ -2316,13 +2316,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.43</v>
+        <v>4.5</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.83</v>
+        <v>4.6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.88</v>
+        <v>5.1</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -2381,25 +2381,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K8" t="n">
         <v>5.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="M8" t="n">
         <v>1.02</v>
@@ -2408,46 +2408,46 @@
         <v>7.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R8" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S8" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="T8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U8" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="V8" t="n">
         <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y8" t="n">
         <v>36</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AA8" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC8" t="n">
         <v>14</v>
@@ -2462,149 +2462,149 @@
         <v>15</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>18</v>
       </c>
-      <c r="AI8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>20</v>
-      </c>
       <c r="AK8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM8" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AO8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV8" t="n">
         <v>8</v>
       </c>
-      <c r="AS8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AW8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD8" t="n">
         <v>8</v>
       </c>
-      <c r="AX8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BE8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="n">
         <v>5.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BN8" t="n">
         <v>5.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BQ8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>10</v>
-      </c>
       <c r="BU8" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -2635,70 +2635,70 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="G9" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
         <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R9" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="T9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="U9" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="V9" t="n">
         <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X9" t="n">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="Y9" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="Z9" t="n">
         <v>55</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>470</v>
       </c>
       <c r="AB9" t="n">
         <v>29</v>
@@ -2707,7 +2707,7 @@
         <v>17</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
         <v>38</v>
@@ -2716,16 +2716,16 @@
         <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK9" t="n">
         <v>17</v>
@@ -2740,125 +2740,125 @@
         <v>4.7</v>
       </c>
       <c r="AO9" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AP9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX9" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AY9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD9" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>14</v>
-      </c>
       <c r="BE9" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="BG9" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="n">
         <v>7.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BL9" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9" t="n">
         <v>6.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BP9" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BR9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -2892,55 +2892,55 @@
         <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J10" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K10" t="n">
         <v>5.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.06</v>
       </c>
       <c r="P10" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X10" t="n">
         <v>950</v>
@@ -2973,7 +2973,7 @@
         <v>17.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="AI10" t="n">
         <v>42</v>
@@ -2982,13 +2982,13 @@
         <v>60</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="AL10" t="n">
         <v>22</v>
       </c>
       <c r="AM10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AN10" t="n">
         <v>8.199999999999999</v>
@@ -2997,22 +2997,22 @@
         <v>7.8</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR10" t="n">
         <v>5.2</v>
       </c>
-      <c r="AR10" t="n">
-        <v>5</v>
-      </c>
       <c r="AS10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT10" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT10" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AU10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV10" t="n">
         <v>12</v>
@@ -3021,19 +3021,19 @@
         <v>16.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY10" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>15</v>
+        <v>4.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC10" t="n">
         <v>17</v>
@@ -3042,77 +3042,77 @@
         <v>15</v>
       </c>
       <c r="BE10" t="n">
-        <v>20</v>
+        <v>5.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BJ10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BR10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
         <v>8</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX10" t="n">
         <v>16</v>
       </c>
-      <c r="BW10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BY10" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BZ10" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -3164,22 +3164,22 @@
         <v>1.49</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="P11" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="S11" t="n">
         <v>5.5</v>
@@ -3188,7 +3188,7 @@
         <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
         <v>1.12</v>
@@ -3197,7 +3197,7 @@
         <v>2.3</v>
       </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Y11" t="n">
         <v>18.5</v>
@@ -3215,7 +3215,7 @@
         <v>9.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE11" t="n">
         <v>700</v>
@@ -3224,7 +3224,7 @@
         <v>8.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>36</v>
@@ -3236,7 +3236,7 @@
         <v>18</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL11" t="n">
         <v>160</v>
@@ -3245,64 +3245,64 @@
         <v>700</v>
       </c>
       <c r="AN11" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO11" t="n">
         <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.4</v>
+        <v>2.96</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="AW11" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BH11" t="n">
         <v>2.86</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -3397,58 +3397,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G12" t="n">
         <v>1.65</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I12" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
         <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="U12" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3463,10 +3463,10 @@
         <v>700</v>
       </c>
       <c r="AB12" t="n">
-        <v>950</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
         <v>950</v>
@@ -3475,10 +3475,10 @@
         <v>700</v>
       </c>
       <c r="AF12" t="n">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AH12" t="n">
         <v>950</v>
@@ -3487,28 +3487,28 @@
         <v>700</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL12" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>500</v>
+        <v>8.6</v>
       </c>
       <c r="AO12" t="n">
         <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.26</v>
+        <v>3.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
         <v>4.2</v>
@@ -3517,55 +3517,55 @@
         <v>4.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.22</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.23</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.2</v>
+        <v>16.5</v>
       </c>
       <c r="AW12" t="n">
         <v>4.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.23</v>
+        <v>9</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.23</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="BA12" t="n">
         <v>4.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.26</v>
+        <v>13.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.25</v>
+        <v>14.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.26</v>
+        <v>2.96</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.27</v>
+        <v>3.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.24</v>
+        <v>7.4</v>
       </c>
       <c r="BG12" t="n">
         <v>4.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK12" t="n">
         <v>1.04</v>
@@ -3577,25 +3577,25 @@
         <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ12" t="n">
         <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS12" t="n">
         <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU12" t="n">
         <v>1.04</v>
@@ -3613,14 +3613,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA12" t="n">
         <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -3651,82 +3651,82 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="M13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.15</v>
       </c>
-      <c r="N13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.16</v>
-      </c>
       <c r="S13" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U13" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="X13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC13" t="n">
         <v>8.4</v>
       </c>
-      <c r="Y13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AD13" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE13" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF13" t="n">
         <v>13.5</v>
@@ -3738,10 +3738,10 @@
         <v>34</v>
       </c>
       <c r="AI13" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ13" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AK13" t="n">
         <v>40</v>
@@ -3750,131 +3750,131 @@
         <v>85</v>
       </c>
       <c r="AM13" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AN13" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AO13" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="AR13" t="n">
         <v>4.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AY13" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="BC13" t="n">
         <v>4.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="BJ13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK13" t="n">
-        <v>6</v>
+        <v>2.44</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>10.5</v>
+        <v>2.98</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BP13" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS13" t="n">
-        <v>9</v>
+        <v>2.86</v>
       </c>
       <c r="BT13" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BV13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.4</v>
+        <v>2.84</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.800000000000001</v>
+        <v>2.92</v>
       </c>
       <c r="BZ13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>9.4</v>
+        <v>3</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -3905,106 +3905,106 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G14" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="I14" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
         <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P14" t="n">
         <v>1.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U14" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA14" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
         <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF14" t="n">
         <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
         <v>75</v>
       </c>
       <c r="AJ14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK14" t="n">
         <v>36</v>
       </c>
-      <c r="AK14" t="n">
-        <v>32</v>
-      </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN14" t="n">
         <v>26</v>
@@ -4013,61 +4013,61 @@
         <v>70</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="AR14" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BI14" t="n">
         <v>2.72</v>
@@ -4076,59 +4076,59 @@
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.3</v>
+        <v>1.92</v>
       </c>
       <c r="BN14" t="n">
-        <v>12.5</v>
+        <v>5.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.59</v>
+        <v>2.24</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.58</v>
+        <v>2.22</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.6</v>
+        <v>2.26</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.59</v>
+        <v>2.24</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -4159,46 +4159,46 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="L15" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="M15" t="n">
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="O15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T15" t="n">
         <v>2.06</v>
@@ -4207,10 +4207,10 @@
         <v>1.83</v>
       </c>
       <c r="V15" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X15" t="n">
         <v>9.800000000000001</v>
@@ -4321,13 +4321,13 @@
         <v>10</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK15" t="n">
         <v>1.04</v>
@@ -4339,10 +4339,10 @@
         <v>1.04</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4357,10 +4357,10 @@
         <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>
@@ -4413,55 +4413,55 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G16" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H16" t="n">
         <v>3.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J16" t="n">
         <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M16" t="n">
         <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>1.45</v>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="U16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
         <v>1.65</v>
@@ -4521,19 +4521,19 @@
         <v>75</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>9.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU16" t="n">
         <v>6.2</v>
@@ -4542,7 +4542,7 @@
         <v>6.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX16" t="n">
         <v>12.5</v>
@@ -4557,22 +4557,22 @@
         <v>10.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.54</v>
+        <v>10</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="BF16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH16" t="n">
         <v>2.94</v>
@@ -4584,59 +4584,59 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.6</v>
+        <v>3.95</v>
       </c>
       <c r="BN16" t="n">
         <v>5.2</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BT16" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.85</v>
+        <v>2.44</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-15 01:00:47</t>
+          <t>2026-06-15 03:07:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
         <v>3.65</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q2" t="n">
         <v>1.79</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
         <v>19</v>
@@ -920,22 +920,22 @@
         <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG2" t="n">
         <v>14.5</v>
@@ -950,10 +950,10 @@
         <v>65</v>
       </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
         <v>75</v>
@@ -962,10 +962,10 @@
         <v>32</v>
       </c>
       <c r="AO2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>11</v>
@@ -974,16 +974,16 @@
         <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
         <v>19</v>
@@ -992,7 +992,7 @@
         <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>13.5</v>
@@ -1004,7 +1004,7 @@
         <v>48</v>
       </c>
       <c r="BC2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD2" t="n">
         <v>36</v>
@@ -1013,10 +1013,10 @@
         <v>55</v>
       </c>
       <c r="BF2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH2" t="n">
         <v>3.75</v>
@@ -1028,13 +1028,13 @@
         <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
@@ -1046,13 +1046,13 @@
         <v>25</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BR2" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BS2" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BT2" t="n">
         <v>5.2</v>
@@ -1061,26 +1061,26 @@
         <v>4.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G3" t="n">
         <v>2.18</v>
       </c>
-      <c r="G3" t="n">
-        <v>2.22</v>
-      </c>
       <c r="H3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.34</v>
@@ -1150,130 +1150,130 @@
         <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AA3" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF3" t="n">
         <v>15.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AI3" t="n">
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>32</v>
       </c>
       <c r="AM3" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW3" t="n">
         <v>32</v>
       </c>
-      <c r="AP3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>26</v>
-      </c>
       <c r="AX3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY3" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BB3" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="BC3" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE3" t="n">
         <v>48</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI3" t="n">
         <v>3.5</v>
@@ -1282,13 +1282,13 @@
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
         <v>5.3</v>
@@ -1303,10 +1303,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BR3" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT3" t="n">
         <v>7</v>
@@ -1318,23 +1318,23 @@
         <v>26</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX3" t="n">
         <v>48</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J4" t="n">
         <v>3.9</v>
@@ -1389,58 +1389,58 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.14</v>
       </c>
       <c r="P4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R4" t="n">
         <v>1.89</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="T4" t="n">
         <v>1.42</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W4" t="n">
         <v>1.44</v>
       </c>
       <c r="X4" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="Y4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z4" t="n">
         <v>22</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>28</v>
       </c>
       <c r="AA4" t="n">
         <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="n">
         <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AF4" t="n">
         <v>36</v>
@@ -1458,28 +1458,28 @@
         <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AL4" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS4" t="n">
         <v>26</v>
@@ -1488,13 +1488,13 @@
         <v>19.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX4" t="n">
         <v>24</v>
@@ -1506,25 +1506,25 @@
         <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB4" t="n">
         <v>42</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BF4" t="n">
         <v>13.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="n">
         <v>5.2</v>
@@ -1536,16 +1536,16 @@
         <v>8.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.96</v>
+        <v>2.24</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO4" t="n">
         <v>5.7</v>
@@ -1554,13 +1554,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4" t="n">
         <v>5.7</v>
@@ -1569,26 +1569,26 @@
         <v>4.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -1619,61 +1619,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.14</v>
+        <v>3.8</v>
       </c>
       <c r="G5" t="n">
-        <v>44</v>
+        <v>4.9</v>
       </c>
       <c r="H5" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="I5" t="n">
-        <v>44</v>
+        <v>2.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.06</v>
+        <v>2.76</v>
       </c>
       <c r="K5" t="n">
-        <v>44</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="P5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.98</v>
       </c>
       <c r="R5" t="n">
         <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1721,88 +1721,88 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.5</v>
+        <v>3.45</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.5</v>
+        <v>2.64</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.5</v>
+        <v>3.65</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.5</v>
+        <v>2.56</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.5</v>
+        <v>2.66</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.5</v>
+        <v>2.74</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.5</v>
+        <v>2.26</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.5</v>
+        <v>2.26</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.5</v>
+        <v>2.26</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.5</v>
+        <v>2.58</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.55</v>
+        <v>2.26</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.55</v>
+        <v>2.48</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.6</v>
+        <v>1.27</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.1</v>
+        <v>1.39</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1814,19 +1814,19 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.9</v>
+        <v>1.37</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.7</v>
+        <v>1.32</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
         <v>1.65</v>
@@ -1897,76 +1897,76 @@
         <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="O6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P6" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="U6" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="X6" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC6" t="n">
         <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AK6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AL6" t="n">
         <v>230</v>
@@ -1975,128 +1975,128 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.6</v>
+        <v>17</v>
       </c>
       <c r="AW6" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX6" t="n">
         <v>5</v>
       </c>
       <c r="AY6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN6" t="n">
         <v>4.9</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD6" t="n">
+      <c r="BO6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>7</v>
       </c>
-      <c r="BE6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
+      <c r="BR6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU6" t="n">
         <v>4.5</v>
       </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -2127,61 +2127,61 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="G7" t="n">
-        <v>8.6</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="J7" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="O7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="R7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
@@ -2229,118 +2229,118 @@
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.02</v>
+        <v>3.95</v>
       </c>
       <c r="AR7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV7" t="n">
         <v>2.3</v>
       </c>
-      <c r="AS7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AW7" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AZ7" t="n">
         <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="BB7" t="n">
         <v>5.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.46</v>
+        <v>2.08</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="BF7" t="n">
         <v>5.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.4</v>
+        <v>2.04</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
         <v>4.3</v>
       </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.5</v>
+        <v>1.36</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.7</v>
+        <v>1.34</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.6</v>
+        <v>1.05</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -2381,52 +2381,52 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I8" t="n">
         <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="M8" t="n">
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P8" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="R8" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="S8" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="U8" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="V8" t="n">
         <v>1.2</v>
@@ -2435,10 +2435,10 @@
         <v>2.68</v>
       </c>
       <c r="X8" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y8" t="n">
         <v>42</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>36</v>
       </c>
       <c r="Z8" t="n">
         <v>120</v>
@@ -2447,164 +2447,164 @@
         <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE8" t="n">
         <v>120</v>
       </c>
       <c r="AF8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
         <v>17.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AO8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV8" t="n">
         <v>9</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AW8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG8" t="n">
         <v>10</v>
       </c>
-      <c r="AS8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>9</v>
-      </c>
       <c r="BH8" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BJ8" t="n">
         <v>9</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BR8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU8" t="n">
         <v>5.7</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -2638,227 +2638,227 @@
         <v>1.76</v>
       </c>
       <c r="G9" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
         <v>4.1</v>
       </c>
       <c r="J9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="P9" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="R9" t="n">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="S9" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="T9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.32</v>
       </c>
-      <c r="U9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.3</v>
-      </c>
       <c r="W9" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X9" t="n">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="Y9" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="Z9" t="n">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AA9" t="n">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="AB9" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AC9" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AD9" t="n">
         <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AG9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT9" t="n">
         <v>16</v>
       </c>
-      <c r="AI9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK9" t="n">
+      <c r="AU9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD9" t="n">
         <v>17</v>
       </c>
-      <c r="AL9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE9" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="BG9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BH9" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO9" t="n">
         <v>5</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.7</v>
       </c>
       <c r="BP9" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BS9" t="n">
         <v>6.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BY9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -2892,61 +2892,61 @@
         <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H10" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I10" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="P10" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U10" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="V10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.63</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.61</v>
       </c>
       <c r="X10" t="n">
         <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="Z10" t="n">
         <v>100</v>
@@ -2955,31 +2955,31 @@
         <v>55</v>
       </c>
       <c r="AB10" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="AE10" t="n">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="AF10" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AG10" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
         <v>42</v>
       </c>
       <c r="AJ10" t="n">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
         <v>48</v>
@@ -2997,122 +2997,122 @@
         <v>7.8</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="AQ10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO10" t="n">
         <v>5.3</v>
       </c>
-      <c r="AR10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU10" t="n">
         <v>5.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>4.9</v>
       </c>
       <c r="BV10" t="n">
         <v>15.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX10" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ10" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="CA10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -3164,13 +3164,13 @@
         <v>1.49</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="O11" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="P11" t="n">
         <v>1.5</v>
@@ -3179,7 +3179,7 @@
         <v>2.48</v>
       </c>
       <c r="R11" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
         <v>5.5</v>
@@ -3197,7 +3197,7 @@
         <v>2.3</v>
       </c>
       <c r="X11" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
         <v>18.5</v>
@@ -3248,61 +3248,61 @@
         <v>18.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>700</v>
+        <v>480</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="AR11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX11" t="n">
         <v>4</v>
       </c>
-      <c r="AS11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AY11" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="BH11" t="n">
         <v>2.86</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G12" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="H12" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I12" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K12" t="n">
         <v>4.6</v>
@@ -3418,40 +3418,40 @@
         <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="X12" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
         <v>950</v>
@@ -3463,31 +3463,31 @@
         <v>700</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="AE12" t="n">
         <v>700</v>
       </c>
       <c r="AF12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG12" t="n">
         <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AI12" t="n">
         <v>700</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="AK12" t="n">
         <v>65</v>
@@ -3499,46 +3499,46 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO12" t="n">
         <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
         <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
         <v>16.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AY12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB12" t="n">
         <v>13.5</v>
@@ -3547,19 +3547,19 @@
         <v>14.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.96</v>
+        <v>7.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="BF12" t="n">
         <v>7.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI12" t="n">
         <v>3</v>
@@ -3568,13 +3568,13 @@
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BN12" t="n">
         <v>4.3</v>
@@ -3586,41 +3586,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR12" t="n">
         <v>25</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -3651,70 +3651,70 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N13" t="n">
         <v>2.28</v>
       </c>
-      <c r="G13" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="O13" t="n">
         <v>1.71</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.68</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
         <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.63</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.68</v>
-      </c>
       <c r="X13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
         <v>7.8</v>
@@ -3723,13 +3723,13 @@
         <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE13" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF13" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG13" t="n">
         <v>14.5</v>
@@ -3741,31 +3741,31 @@
         <v>150</v>
       </c>
       <c r="AJ13" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AK13" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AL13" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AM13" t="n">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="AN13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AO13" t="n">
         <v>220</v>
       </c>
       <c r="AP13" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS13" t="n">
         <v>4.9</v>
@@ -3783,98 +3783,98 @@
         <v>4.9</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD13" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD13" t="n">
+      <c r="BE13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF13" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>29</v>
       </c>
       <c r="BG13" t="n">
         <v>5</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="BJ13" t="n">
         <v>13</v>
       </c>
       <c r="BK13" t="n">
-        <v>2.44</v>
+        <v>6.6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.98</v>
+        <v>2.06</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS13" t="n">
-        <v>2.86</v>
+        <v>11</v>
       </c>
       <c r="BT13" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>2.84</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.92</v>
+        <v>11.5</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>3</v>
+        <v>11.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G14" t="n">
         <v>2.38</v>
       </c>
       <c r="H14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -3932,16 +3932,16 @@
         <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
         <v>4.3</v>
@@ -3950,7 +3950,7 @@
         <v>1.88</v>
       </c>
       <c r="U14" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
         <v>1.35</v>
@@ -3965,19 +3965,19 @@
         <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA14" t="n">
         <v>85</v>
       </c>
       <c r="AB14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
         <v>70</v>
@@ -3992,13 +3992,13 @@
         <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ14" t="n">
         <v>34</v>
       </c>
       <c r="AK14" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AL14" t="n">
         <v>60</v>
@@ -4007,88 +4007,88 @@
         <v>140</v>
       </c>
       <c r="AN14" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AO14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AQ14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX14" t="n">
         <v>5.1</v>
       </c>
-      <c r="AR14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT14" t="n">
+      <c r="AY14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC14" t="n">
         <v>4.7</v>
       </c>
-      <c r="AU14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD14" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="BN14" t="n">
         <v>5.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4100,35 +4100,35 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
       <c r="BT14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.22</v>
+        <v>3.05</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>2.02</v>
       </c>
       <c r="G15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H15" t="n">
         <v>4.7</v>
@@ -4177,7 +4177,7 @@
         <v>3.35</v>
       </c>
       <c r="L15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M15" t="n">
         <v>1.11</v>
@@ -4186,13 +4186,13 @@
         <v>2.96</v>
       </c>
       <c r="O15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P15" t="n">
         <v>1.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
         <v>1.23</v>
@@ -4264,10 +4264,10 @@
         <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ15" t="n">
         <v>12</v>
@@ -4285,10 +4285,10 @@
         <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX15" t="n">
         <v>9.800000000000001</v>
@@ -4297,16 +4297,16 @@
         <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB15" t="n">
         <v>21</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="BD15" t="n">
         <v>9</v>
@@ -4315,7 +4315,7 @@
         <v>10</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="BG15" t="n">
         <v>10</v>
@@ -4324,37 +4324,37 @@
         <v>2.9</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="BJ15" t="n">
         <v>11.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN15" t="n">
         <v>4.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT15" t="n">
         <v>7.8</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G16" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I16" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J16" t="n">
         <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.52</v>
@@ -4443,28 +4443,28 @@
         <v>1.45</v>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
         <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U16" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X16" t="n">
         <v>15.5</v>
@@ -4476,13 +4476,13 @@
         <v>34</v>
       </c>
       <c r="AA16" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB16" t="n">
         <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD16" t="n">
         <v>22</v>
@@ -4503,7 +4503,7 @@
         <v>100</v>
       </c>
       <c r="AJ16" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AK16" t="n">
         <v>32</v>
@@ -4521,7 +4521,7 @@
         <v>75</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>9.6</v>
@@ -4530,7 +4530,7 @@
         <v>8</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT16" t="n">
         <v>7.6</v>
@@ -4539,40 +4539,40 @@
         <v>6.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AX16" t="n">
         <v>12.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ16" t="n">
         <v>16.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BB16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG16" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>4.7</v>
       </c>
       <c r="BH16" t="n">
         <v>2.94</v>
@@ -4626,7 +4626,7 @@
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.44</v>
+        <v>3.95</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-15 03:07:48</t>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,61 +860,61 @@
         <v>3.5</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H2" t="n">
         <v>2.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S2" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U2" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
         <v>16</v>
@@ -941,31 +941,31 @@
         <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
         <v>32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>11</v>
@@ -974,13 +974,13 @@
         <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
         <v>9.800000000000001</v>
@@ -989,7 +989,7 @@
         <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY2" t="n">
         <v>13.5</v>
@@ -998,7 +998,7 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB2" t="n">
         <v>48</v>
@@ -1007,25 +1007,25 @@
         <v>30</v>
       </c>
       <c r="BD2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
         <v>55</v>
       </c>
       <c r="BF2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BG2" t="n">
         <v>12</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK2" t="n">
         <v>6</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
@@ -1046,13 +1046,13 @@
         <v>25</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT2" t="n">
         <v>5.2</v>
@@ -1064,23 +1064,23 @@
         <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1144,19 +1144,19 @@
         <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U3" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
         <v>1.37</v>
@@ -1165,7 +1165,7 @@
         <v>1.84</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
         <v>17</v>
@@ -1177,10 +1177,10 @@
         <v>65</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>14.5</v>
@@ -1189,28 +1189,28 @@
         <v>38</v>
       </c>
       <c r="AF3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
         <v>15.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
         <v>32</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="AN3" t="n">
         <v>12.5</v>
@@ -1225,7 +1225,7 @@
         <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
         <v>50</v>
@@ -1261,22 +1261,22 @@
         <v>18.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG3" t="n">
         <v>26</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ3" t="n">
         <v>9</v>
@@ -1285,7 +1285,7 @@
         <v>5.7</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM3" t="n">
         <v>13</v>
@@ -1297,13 +1297,13 @@
         <v>4.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BS3" t="n">
         <v>9.6</v>
@@ -1312,7 +1312,7 @@
         <v>7</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BV3" t="n">
         <v>26</v>
@@ -1321,20 +1321,20 @@
         <v>9.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BY3" t="n">
         <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA3" t="n">
         <v>8.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
@@ -1371,49 +1371,49 @@
         <v>3.25</v>
       </c>
       <c r="H4" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="I4" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="S4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W4" t="n">
         <v>1.44</v>
@@ -1422,7 +1422,7 @@
         <v>95</v>
       </c>
       <c r="Y4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Z4" t="n">
         <v>22</v>
@@ -1431,16 +1431,16 @@
         <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
         <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AF4" t="n">
         <v>36</v>
@@ -1452,7 +1452,7 @@
         <v>13.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ4" t="n">
         <v>500</v>
@@ -1461,22 +1461,22 @@
         <v>48</v>
       </c>
       <c r="AL4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AR4" t="n">
         <v>16.5</v>
@@ -1485,10 +1485,10 @@
         <v>26</v>
       </c>
       <c r="AT4" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AU4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
@@ -1497,7 +1497,7 @@
         <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY4" t="n">
         <v>12.5</v>
@@ -1515,37 +1515,37 @@
         <v>22</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BF4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.24</v>
+        <v>11.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO4" t="n">
         <v>5.7</v>
@@ -1554,16 +1554,16 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BU4" t="n">
         <v>4.7</v>
@@ -1572,23 +1572,23 @@
         <v>14</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA4" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
@@ -1619,58 +1619,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J5" t="n">
         <v>2.76</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="M5" t="n">
         <v>1.16</v>
       </c>
       <c r="N5" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="O5" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="P5" t="n">
         <v>1.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
         <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V5" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W5" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X5" t="n">
         <v>15.5</v>
@@ -1727,58 +1727,58 @@
         <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AT5" t="n">
         <v>4.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX5" t="n">
         <v>2.56</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>2.66</v>
       </c>
       <c r="AY5" t="n">
         <v>2.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="BH5" t="n">
         <v>2.56</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -1885,31 +1885,31 @@
         <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="K6" t="n">
         <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="O6" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P6" t="n">
         <v>1.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="R6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S6" t="n">
         <v>6.4</v>
@@ -1918,22 +1918,22 @@
         <v>2.26</v>
       </c>
       <c r="U6" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X6" t="n">
         <v>7.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
@@ -1945,7 +1945,7 @@
         <v>7.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>500</v>
@@ -1954,31 +1954,31 @@
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK6" t="n">
         <v>36</v>
       </c>
-      <c r="AK6" t="n">
-        <v>38</v>
-      </c>
       <c r="AL6" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO6" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AP6" t="n">
         <v>6.2</v>
@@ -1987,55 +1987,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU6" t="n">
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AZ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB6" t="n">
         <v>7.2</v>
       </c>
-      <c r="BA6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BC6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF6" t="n">
         <v>7.4</v>
       </c>
-      <c r="BE6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG6" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BI6" t="n">
         <v>2.14</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
         <v>4.9</v>
@@ -2086,17 +2086,17 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>2.54</v>
       </c>
       <c r="G7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
         <v>3</v>
@@ -2145,7 +2145,7 @@
         <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M7" t="n">
         <v>1.15</v>
@@ -2154,13 +2154,13 @@
         <v>2.24</v>
       </c>
       <c r="O7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="R7" t="n">
         <v>1.13</v>
@@ -2169,7 +2169,7 @@
         <v>6.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
         <v>1.6</v>
@@ -2241,10 +2241,10 @@
         <v>3.95</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AT7" t="n">
         <v>3.75</v>
@@ -2253,40 +2253,40 @@
         <v>3.65</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AX7" t="n">
         <v>1.97</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AZ7" t="n">
         <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="BB7" t="n">
         <v>5.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BF7" t="n">
         <v>5.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="BH7" t="n">
         <v>2.6</v>
@@ -2322,7 +2322,7 @@
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
@@ -2340,24 +2340,24 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,244 +2367,244 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Selfoss</t>
+          <t>Ymir</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="G8" t="n">
-        <v>1.59</v>
+        <v>2.08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="P8" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="R8" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="U8" t="n">
-        <v>2.84</v>
+        <v>3.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>2.68</v>
+        <v>1.92</v>
       </c>
       <c r="X8" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y8" t="n">
         <v>55</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB8" t="n">
         <v>42</v>
       </c>
-      <c r="Z8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>21</v>
-      </c>
       <c r="AC8" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AD8" t="n">
         <v>24</v>
       </c>
       <c r="AE8" t="n">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="AF8" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="AG8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY8" t="n">
         <v>12</v>
       </c>
-      <c r="AH8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="AZ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP8" t="n">
         <v>13</v>
       </c>
-      <c r="AV8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW8" t="n">
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
         <v>23</v>
       </c>
-      <c r="AX8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ8" t="n">
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
         <v>7.6</v>
       </c>
-      <c r="BA8" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN8" t="n">
+      <c r="CA8" t="n">
         <v>5.3</v>
       </c>
-      <c r="BO8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>5</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
@@ -2626,166 +2626,166 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fjolnir</t>
+          <t>Selfoss</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kari</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="I9" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K9" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="Q9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.2</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.32</v>
-      </c>
       <c r="W9" t="n">
-        <v>2.22</v>
+        <v>2.68</v>
       </c>
       <c r="X9" t="n">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="Y9" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="Z9" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="AA9" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM9" t="n">
         <v>500</v>
       </c>
-      <c r="AB9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="AN9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AO9" t="n">
         <v>29</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>12</v>
       </c>
       <c r="AP9" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BB9" t="n">
         <v>15.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BE9" t="n">
         <v>21</v>
@@ -2794,19 +2794,19 @@
         <v>3.65</v>
       </c>
       <c r="BG9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BI9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK9" t="n">
         <v>5.2</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2815,57 +2815,57 @@
         <v>10</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BP9" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BS9" t="n">
         <v>6.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV9" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BW9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY9" t="n">
         <v>8.6</v>
       </c>
-      <c r="BX9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BY9" t="n">
+      <c r="BZ9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>6.4</v>
-      </c>
       <c r="CA9" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KH Hlidarendi</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="G10" t="n">
-        <v>2.58</v>
+        <v>1.79</v>
       </c>
       <c r="H10" t="n">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K10" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
+        <v>16</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X10" t="n">
+        <v>170</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>150</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>190</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>470</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW10" t="n">
         <v>16.5</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="AX10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN10" t="n">
         <v>6.8</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X10" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>950</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AN10" t="n">
+      <c r="BO10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="BX10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BY10" t="n">
         <v>7.8</v>
       </c>
-      <c r="AP10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BI10" t="n">
+      <c r="BZ10" t="n">
         <v>6.2</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>5.7</v>
-      </c>
       <c r="CA10" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Argentinian Torneo A</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sportivo Belgrano</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Def Belgrano VR</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.59</v>
+        <v>2.38</v>
       </c>
       <c r="G11" t="n">
-        <v>1.76</v>
+        <v>2.54</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>2.36</v>
       </c>
       <c r="I11" t="n">
-        <v>8.800000000000001</v>
+        <v>2.52</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.49</v>
+        <v>1.09</v>
       </c>
       <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.11</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.48</v>
-      </c>
       <c r="R11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T11" t="n">
         <v>1.18</v>
       </c>
-      <c r="S11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.4</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>5.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.12</v>
+        <v>1.65</v>
       </c>
       <c r="W11" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="X11" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY11" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
         <v>8.6</v>
       </c>
-      <c r="AG11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>480</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="BN11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO11" t="n">
         <v>5.4</v>
       </c>
-      <c r="AR11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>2.88</v>
-      </c>
       <c r="BP11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BR11" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.12</v>
+        <v>6.8</v>
       </c>
       <c r="BT11" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU11" t="n">
         <v>5.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.18</v>
+        <v>7.2</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Torneo A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,219 +3383,219 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Sportivo Belgrano</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>Def Belgrano VR</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="G12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
         <v>4.1</v>
       </c>
-      <c r="K12" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.84</v>
+        <v>2.62</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="S12" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>2.54</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="W12" t="n">
         <v>2.44</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="n">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AA12" t="n">
         <v>700</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AE12" t="n">
         <v>700</v>
       </c>
       <c r="AF12" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AI12" t="n">
         <v>700</v>
       </c>
       <c r="AJ12" t="n">
-        <v>120</v>
+        <v>16.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
         <v>160</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ12" t="n">
         <v>15</v>
       </c>
-      <c r="AR12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY12" t="n">
+      <c r="BK12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS12" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BT12" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BU12" t="n">
         <v>5.8</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BZ12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
@@ -3637,228 +3637,228 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>Maranhao</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.46</v>
+        <v>1.63</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="H13" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="I13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J13" t="n">
         <v>4.1</v>
       </c>
-      <c r="J13" t="n">
-        <v>2.72</v>
-      </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.18</v>
       </c>
-      <c r="N13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.63</v>
+        <v>2.44</v>
       </c>
       <c r="X13" t="n">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>120</v>
       </c>
-      <c r="AB13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AK13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU13" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AV13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC13" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>350</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP13" t="n">
+      <c r="BD13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU13" t="n">
         <v>5.8</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>25</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS13" t="n">
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
         <v>11</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>10</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
@@ -3867,14 +3867,14 @@
         <v>11.5</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA13" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
@@ -3896,246 +3896,246 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="G14" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>2.34</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="P14" t="n">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.26</v>
+        <v>3.15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="X14" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF14" t="n">
         <v>16</v>
       </c>
-      <c r="Z14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>970</v>
-      </c>
       <c r="AG14" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AI14" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AJ14" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AK14" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>290</v>
       </c>
       <c r="AN14" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU14" t="n">
         <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="AX14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU14" t="n">
         <v>5.1</v>
       </c>
-      <c r="AY14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW14" t="n">
-        <v>3.05</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.02</v>
+        <v>10.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.1</v>
+        <v>10.5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,244 +4145,244 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
         <v>2.02</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="X15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>12</v>
-      </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>10.5</v>
+        <v>3.3</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>
@@ -4404,239 +4404,493 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="G16" t="n">
-        <v>2.56</v>
+        <v>2.06</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M16" t="n">
         <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="O16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.25</v>
       </c>
-      <c r="S16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>1.94</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.64</v>
-      </c>
       <c r="X16" t="n">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="Z16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AB16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AF16" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ16" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AL16" t="n">
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW16" t="n">
         <v>9.6</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AX16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>8</v>
       </c>
-      <c r="AS16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BA16" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="BC16" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="BD16" t="n">
         <v>9</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT16" t="n">
         <v>8</v>
       </c>
-      <c r="BG16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BN16" t="n">
+      <c r="BU16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>11</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-15 07:22:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BN17" t="n">
         <v>5.2</v>
       </c>
-      <c r="BO16" t="n">
+      <c r="BO17" t="n">
         <v>4.6</v>
       </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT16" t="n">
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BT17" t="n">
         <v>6.4</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="BU17" t="n">
         <v>5.7</v>
       </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>2026-06-15 05:15:13</t>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G2" t="n">
         <v>3.5</v>
       </c>
-      <c r="G2" t="n">
-        <v>3.65</v>
-      </c>
       <c r="H2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -881,40 +881,40 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="T2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V2" t="n">
         <v>1.81</v>
       </c>
       <c r="W2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X2" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
         <v>16</v>
@@ -926,7 +926,7 @@
         <v>17</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>10.5</v>
@@ -935,7 +935,7 @@
         <v>21</v>
       </c>
       <c r="AF2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG2" t="n">
         <v>14.5</v>
@@ -953,22 +953,22 @@
         <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP2" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
         <v>14</v>
@@ -992,7 +992,7 @@
         <v>24</v>
       </c>
       <c r="AY2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
         <v>13.5</v>
@@ -1004,34 +1004,34 @@
         <v>48</v>
       </c>
       <c r="BC2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD2" t="n">
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BF2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BG2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM2" t="n">
         <v>15.5</v>
@@ -1043,16 +1043,16 @@
         <v>6</v>
       </c>
       <c r="BP2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT2" t="n">
         <v>5.2</v>
@@ -1064,23 +1064,23 @@
         <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>26</v>
       </c>
       <c r="BY2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="G3" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.35</v>
@@ -1135,10 +1135,10 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
         <v>2.28</v>
@@ -1147,61 +1147,61 @@
         <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="X3" t="n">
         <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH3" t="n">
         <v>15</v>
       </c>
-      <c r="AG3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK3" t="n">
         <v>22</v>
@@ -1213,67 +1213,67 @@
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AO3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS3" t="n">
         <v>50</v>
       </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX3" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE3" t="n">
         <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI3" t="n">
         <v>3.55</v>
@@ -1288,53 +1288,53 @@
         <v>90</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO3" t="n">
         <v>4.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BV3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BW3" t="n">
         <v>9.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY3" t="n">
         <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -1383,13 +1383,13 @@
         <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.13</v>
@@ -1398,49 +1398,49 @@
         <v>3.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R4" t="n">
         <v>1.92</v>
       </c>
       <c r="S4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T4" t="n">
         <v>1.41</v>
       </c>
       <c r="U4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V4" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="W4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X4" t="n">
         <v>95</v>
       </c>
       <c r="Y4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB4" t="n">
         <v>26</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>36</v>
       </c>
       <c r="AC4" t="n">
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
         <v>36</v>
@@ -1452,7 +1452,7 @@
         <v>13.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AJ4" t="n">
         <v>500</v>
@@ -1467,67 +1467,67 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ4" t="n">
         <v>17</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW4" t="n">
         <v>17</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>16</v>
       </c>
       <c r="AX4" t="n">
         <v>25</v>
       </c>
       <c r="AY4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BB4" t="n">
         <v>42</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD4" t="n">
         <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI4" t="n">
         <v>4.3</v>
@@ -1536,13 +1536,13 @@
         <v>8.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BN4" t="n">
         <v>7.2</v>
@@ -1551,44 +1551,44 @@
         <v>5.7</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR4" t="n">
         <v>23</v>
       </c>
       <c r="BS4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU4" t="n">
         <v>4.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ4" t="n">
         <v>11</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -1637,40 +1637,40 @@
         <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="P5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T5" t="n">
         <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
         <v>15.5</v>
@@ -1727,82 +1727,82 @@
         <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="AW5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AX5" t="n">
         <v>2.5</v>
       </c>
-      <c r="AX5" t="n">
-        <v>2.56</v>
-      </c>
       <c r="AY5" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BD5" t="n">
         <v>1.99</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BF5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BG5" t="n">
         <v>2.02</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2</v>
       </c>
       <c r="BH5" t="n">
         <v>2.56</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1814,19 +1814,19 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1879,13 @@
         <v>2.4</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
         <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="K6" t="n">
         <v>3.15</v>
@@ -1900,13 +1900,13 @@
         <v>2.34</v>
       </c>
       <c r="O6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P6" t="n">
         <v>1.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R6" t="n">
         <v>1.15</v>
@@ -1915,16 +1915,16 @@
         <v>6.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V6" t="n">
         <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X6" t="n">
         <v>7.8</v>
@@ -1984,13 +1984,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
         <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT6" t="n">
         <v>5.5</v>
@@ -2005,10 +2005,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
         <v>12.5</v>
@@ -2029,7 +2029,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG6" t="n">
         <v>8.6</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
         <v>3.1</v>
@@ -2139,10 +2139,10 @@
         <v>3.75</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
         <v>1.66</v>
@@ -2151,16 +2151,16 @@
         <v>1.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="R7" t="n">
         <v>1.13</v>
@@ -2172,7 +2172,7 @@
         <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V7" t="n">
         <v>1.37</v>
@@ -2181,7 +2181,7 @@
         <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
@@ -2235,16 +2235,16 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AQ7" t="n">
         <v>3.95</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="AT7" t="n">
         <v>3.75</v>
@@ -2253,58 +2253,58 @@
         <v>3.65</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AZ7" t="n">
         <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.3</v>
+        <v>1.75</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BF7" t="n">
         <v>5.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="BH7" t="n">
         <v>2.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
@@ -2316,7 +2316,7 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2328,29 +2328,29 @@
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.06</v>
@@ -2414,7 +2414,7 @@
         <v>4.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="R8" t="n">
         <v>2.5</v>
@@ -2426,13 +2426,13 @@
         <v>1.27</v>
       </c>
       <c r="U8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="X8" t="n">
         <v>100</v>
@@ -2447,7 +2447,7 @@
         <v>85</v>
       </c>
       <c r="AB8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AC8" t="n">
         <v>22</v>
@@ -2483,64 +2483,64 @@
         <v>36</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO8" t="n">
         <v>13</v>
       </c>
       <c r="AP8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT8" t="n">
         <v>4</v>
       </c>
-      <c r="AR8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AU8" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AV8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW8" t="n">
         <v>25</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.85</v>
+        <v>20</v>
       </c>
       <c r="AY8" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BC8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BF8" t="n">
         <v>3.65</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH8" t="n">
         <v>8.199999999999999</v>
@@ -2558,10 +2558,10 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO8" t="n">
         <v>5</v>
@@ -2570,31 +2570,31 @@
         <v>13</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BR8" t="n">
         <v>15.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV8" t="n">
         <v>23</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BX8" t="n">
         <v>21</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BZ8" t="n">
         <v>7.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H9" t="n">
         <v>5.3</v>
@@ -2647,7 +2647,7 @@
         <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K9" t="n">
         <v>6</v>
@@ -2665,19 +2665,19 @@
         <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q9" t="n">
         <v>1.31</v>
       </c>
       <c r="R9" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
         <v>1.79</v>
       </c>
       <c r="T9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U9" t="n">
         <v>2.88</v>
@@ -2692,7 +2692,7 @@
         <v>55</v>
       </c>
       <c r="Y9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z9" t="n">
         <v>120</v>
@@ -2710,10 +2710,10 @@
         <v>24</v>
       </c>
       <c r="AE9" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
         <v>12</v>
@@ -2722,7 +2722,7 @@
         <v>17.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="n">
         <v>18.5</v>
@@ -2731,16 +2731,16 @@
         <v>14.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AN9" t="n">
         <v>4.2</v>
       </c>
       <c r="AO9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AP9" t="n">
         <v>10.5</v>
@@ -2749,10 +2749,10 @@
         <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>17.5</v>
@@ -2767,13 +2767,13 @@
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY9" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="BA9" t="n">
         <v>23</v>
@@ -2788,13 +2788,13 @@
         <v>18</v>
       </c>
       <c r="BE9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BF9" t="n">
         <v>3.65</v>
       </c>
       <c r="BG9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BH9" t="n">
         <v>6.4</v>
@@ -2806,16 +2806,16 @@
         <v>9</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO9" t="n">
         <v>4.2</v>
@@ -2824,41 +2824,41 @@
         <v>9.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR9" t="n">
         <v>16</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT9" t="n">
         <v>10.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX9" t="n">
         <v>30</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="G10" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="H10" t="n">
         <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K10" t="n">
         <v>6</v>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.05</v>
@@ -2922,37 +2922,37 @@
         <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="R10" t="n">
         <v>3.05</v>
       </c>
       <c r="S10" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T10" t="n">
         <v>1.25</v>
       </c>
       <c r="U10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X10" t="n">
         <v>170</v>
       </c>
       <c r="Y10" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="Z10" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="AA10" t="n">
-        <v>470</v>
+        <v>170</v>
       </c>
       <c r="AB10" t="n">
         <v>44</v>
@@ -2961,7 +2961,7 @@
         <v>24</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
         <v>40</v>
@@ -2976,28 +2976,28 @@
         <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ10" t="n">
         <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL10" t="n">
         <v>18.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AO10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
         <v>18</v>
@@ -3006,16 +3006,16 @@
         <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT10" t="n">
         <v>17</v>
       </c>
       <c r="AU10" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
         <v>16.5</v>
@@ -3045,74 +3045,74 @@
         <v>20</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BG10" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK10" t="n">
         <v>5.2</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5</v>
-      </c>
       <c r="BL10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BN10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW10" t="n">
+      <c r="BX10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BY10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BX10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="CA10" t="n">
         <v>4.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.38</v>
       </c>
       <c r="G11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H11" t="n">
         <v>2.36</v>
@@ -3155,7 +3155,7 @@
         <v>2.52</v>
       </c>
       <c r="J11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
         <v>5.8</v>
@@ -3173,7 +3173,7 @@
         <v>1.03</v>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>1.11</v>
@@ -3188,13 +3188,13 @@
         <v>1.18</v>
       </c>
       <c r="U11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="V11" t="n">
         <v>1.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X11" t="n">
         <v>950</v>
@@ -3227,7 +3227,7 @@
         <v>26</v>
       </c>
       <c r="AH11" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AI11" t="n">
         <v>42</v>
@@ -3245,37 +3245,37 @@
         <v>23</v>
       </c>
       <c r="AN11" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AO11" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
         <v>9.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY11" t="n">
         <v>10.5</v>
@@ -3287,86 +3287,86 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="BF11" t="n">
         <v>4.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH11" t="n">
         <v>12.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BJ11" t="n">
         <v>8</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BP11" t="n">
         <v>16</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR11" t="n">
         <v>14</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV11" t="n">
         <v>16</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX11" t="n">
         <v>14</v>
       </c>
       <c r="BY11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="CA11" t="n">
         <v>3.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
         <v>4.1</v>
@@ -3421,19 +3421,19 @@
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="O12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
         <v>5.5</v>
@@ -3442,7 +3442,7 @@
         <v>2.54</v>
       </c>
       <c r="U12" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
         <v>1.11</v>
@@ -3457,7 +3457,7 @@
         <v>19.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AA12" t="n">
         <v>700</v>
@@ -3466,7 +3466,7 @@
         <v>5.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
         <v>40</v>
@@ -3490,16 +3490,16 @@
         <v>16.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
         <v>160</v>
       </c>
       <c r="AM12" t="n">
-        <v>700</v>
+        <v>410</v>
       </c>
       <c r="AN12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
@@ -3511,34 +3511,34 @@
         <v>6</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU12" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4.5</v>
       </c>
       <c r="AV12" t="n">
         <v>7.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX12" t="n">
         <v>6.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ12" t="n">
         <v>7.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
@@ -3547,16 +3547,16 @@
         <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF12" t="n">
         <v>14</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH12" t="n">
         <v>2.82</v>
@@ -3580,7 +3580,7 @@
         <v>3.85</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP12" t="n">
         <v>12.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -3651,64 +3651,64 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H13" t="n">
         <v>5.7</v>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N13" t="n">
         <v>4.5</v>
       </c>
-      <c r="L13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="T13" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V13" t="n">
         <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="Z13" t="n">
         <v>500</v>
@@ -3717,10 +3717,10 @@
         <v>700</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
         <v>29</v>
@@ -3729,37 +3729,37 @@
         <v>700</v>
       </c>
       <c r="AF13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
         <v>700</v>
       </c>
       <c r="AJ13" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="AK13" t="n">
         <v>65</v>
       </c>
       <c r="AL13" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO13" t="n">
         <v>700</v>
       </c>
       <c r="AP13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>15</v>
@@ -3774,13 +3774,13 @@
         <v>7.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV13" t="n">
         <v>16.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX13" t="n">
         <v>8.6</v>
@@ -3792,7 +3792,7 @@
         <v>7</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB13" t="n">
         <v>13.5</v>
@@ -3801,80 +3801,80 @@
         <v>14.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13" t="n">
         <v>7.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BN13" t="n">
         <v>4.3</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BP13" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU13" t="n">
         <v>6</v>
       </c>
-      <c r="BR13" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BZ13" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -3905,172 +3905,172 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="G14" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="K14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="N14" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="O14" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="P14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
         <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="T14" t="n">
         <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="W14" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="X14" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>10</v>
       </c>
-      <c r="Z14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH14" t="n">
+      <c r="AR14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF14" t="n">
         <v>32</v>
       </c>
-      <c r="AI14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>29</v>
-      </c>
       <c r="BG14" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BJ14" t="n">
         <v>13</v>
@@ -4082,43 +4082,43 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BP14" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BV14" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -4159,70 +4159,70 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G15" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="X15" t="n">
         <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
         <v>30</v>
       </c>
       <c r="AA15" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AB15" t="n">
         <v>11</v>
@@ -4231,7 +4231,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
         <v>70</v>
@@ -4246,7 +4246,7 @@
         <v>24</v>
       </c>
       <c r="AI15" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ15" t="n">
         <v>34</v>
@@ -4261,22 +4261,22 @@
         <v>140</v>
       </c>
       <c r="AN15" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
         <v>80</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AR15" t="n">
         <v>19</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT15" t="n">
         <v>6.2</v>
@@ -4285,64 +4285,64 @@
         <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AW15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA15" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4354,35 +4354,35 @@
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>2.06</v>
       </c>
       <c r="H16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
         <v>5</v>
@@ -4437,25 +4437,25 @@
         <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>1.47</v>
       </c>
       <c r="P16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
         <v>1.83</v>
@@ -4464,7 +4464,7 @@
         <v>1.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X16" t="n">
         <v>9.800000000000001</v>
@@ -4488,7 +4488,7 @@
         <v>25</v>
       </c>
       <c r="AE16" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AF16" t="n">
         <v>11.5</v>
@@ -4527,22 +4527,22 @@
         <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU16" t="n">
         <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>17.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX16" t="n">
         <v>9.800000000000001</v>
@@ -4551,19 +4551,19 @@
         <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8</v>
+        <v>19.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
       </c>
       <c r="BC16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BD16" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="BE16" t="n">
         <v>10</v>
@@ -4572,46 +4572,46 @@
         <v>19</v>
       </c>
       <c r="BG16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ16" t="n">
         <v>11.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN16" t="n">
         <v>4.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BP16" t="n">
         <v>16</v>
       </c>
       <c r="BQ16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT16" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>8</v>
       </c>
       <c r="BU16" t="n">
         <v>5.3</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
         <v>11.5</v>
       </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>11</v>
-      </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
         <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L17" t="n">
         <v>1.53</v>
@@ -4691,16 +4691,16 @@
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P17" t="n">
         <v>1.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R17" t="n">
         <v>1.24</v>
@@ -4709,7 +4709,7 @@
         <v>4.8</v>
       </c>
       <c r="T17" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>1.9</v>
@@ -4727,106 +4727,106 @@
         <v>12.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AA17" t="n">
         <v>85</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AC17" t="n">
         <v>7.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF17" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
         <v>970</v>
       </c>
       <c r="AI17" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK17" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL17" t="n">
         <v>65</v>
       </c>
       <c r="AM17" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD17" t="n">
         <v>46</v>
       </c>
-      <c r="AO17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX17" t="n">
+      <c r="BE17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG17" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BH17" t="n">
         <v>2.88</v>
@@ -4844,7 +4844,7 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>2.34</v>
+        <v>1.4</v>
       </c>
       <c r="BN17" t="n">
         <v>5.2</v>
@@ -4856,7 +4856,7 @@
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
@@ -4880,17 +4880,17 @@
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -857,55 +857,55 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
         <v>3.5</v>
       </c>
       <c r="H2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I2" t="n">
         <v>2.24</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R2" t="n">
         <v>1.52</v>
       </c>
       <c r="S2" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U2" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
         <v>1.4</v>
@@ -920,7 +920,7 @@
         <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB2" t="n">
         <v>17</v>
@@ -941,7 +941,7 @@
         <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI2" t="n">
         <v>32</v>
@@ -965,7 +965,7 @@
         <v>13</v>
       </c>
       <c r="AP2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
         <v>11.5</v>
@@ -980,31 +980,31 @@
         <v>15.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW2" t="n">
         <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
         <v>27</v>
       </c>
       <c r="BB2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD2" t="n">
         <v>34</v>
@@ -1028,13 +1028,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BL2" t="n">
         <v>90</v>
       </c>
       <c r="BM2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
@@ -1046,13 +1046,13 @@
         <v>24</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BR2" t="n">
         <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT2" t="n">
         <v>5.2</v>
@@ -1064,23 +1064,23 @@
         <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BX2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>2.24</v>
       </c>
       <c r="G3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.8</v>
@@ -1135,40 +1135,40 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
         <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U3" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V3" t="n">
         <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z3" t="n">
         <v>26</v>
@@ -1177,7 +1177,7 @@
         <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
         <v>8.4</v>
@@ -1189,10 +1189,10 @@
         <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
         <v>15</v>
@@ -1204,7 +1204,7 @@
         <v>29</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
         <v>32</v>
@@ -1219,7 +1219,7 @@
         <v>27</v>
       </c>
       <c r="AP3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>14.5</v>
@@ -1243,10 +1243,10 @@
         <v>30</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
@@ -1255,7 +1255,7 @@
         <v>34</v>
       </c>
       <c r="BB3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC3" t="n">
         <v>19.5</v>
@@ -1273,7 +1273,7 @@
         <v>24</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI3" t="n">
         <v>3.55</v>
@@ -1282,31 +1282,31 @@
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>90</v>
       </c>
       <c r="BM3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
         <v>5.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP3" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>6.8</v>
@@ -1318,23 +1318,23 @@
         <v>24</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="BX3" t="n">
         <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>19.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="I4" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
         <v>4.3</v>
@@ -1389,22 +1389,22 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
         <v>1.41</v>
@@ -1413,13 +1413,13 @@
         <v>3.25</v>
       </c>
       <c r="V4" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="W4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="X4" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="Y4" t="n">
         <v>20</v>
@@ -1428,103 +1428,103 @@
         <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AB4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
         <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AF4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
         <v>13.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AK4" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AL4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AT4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV4" t="n">
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC4" t="n">
         <v>25</v>
       </c>
-      <c r="AY4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>24</v>
-      </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="n">
         <v>5.4</v>
@@ -1536,16 +1536,16 @@
         <v>8.4</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO4" t="n">
         <v>5.7</v>
@@ -1554,13 +1554,13 @@
         <v>20</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR4" t="n">
         <v>23</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT4" t="n">
         <v>5.9</v>
@@ -1572,23 +1572,23 @@
         <v>13.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
         <v>19</v>
       </c>
       <c r="BY4" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -1619,37 +1619,37 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.65</v>
+        <v>2.86</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="I5" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="J5" t="n">
         <v>2.76</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="M5" t="n">
         <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="O5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="P5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q5" t="n">
         <v>3.1</v>
@@ -1658,19 +1658,19 @@
         <v>1.13</v>
       </c>
       <c r="S5" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="W5" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="X5" t="n">
         <v>15.5</v>
@@ -1700,7 +1700,7 @@
         <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
         <v>950</v>
@@ -1724,85 +1724,85 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AT5" t="n">
         <v>3.7</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AX5" t="n">
         <v>3.55</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AY5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>3.8</v>
       </c>
-      <c r="AS5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BA5" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="BB5" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.06</v>
+        <v>2.54</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.99</v>
+        <v>2.52</v>
       </c>
       <c r="BE5" t="n">
         <v>2.56</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.1</v>
+        <v>1.76</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1814,19 +1814,19 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
         <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="K6" t="n">
         <v>3.15</v>
@@ -1897,16 +1897,16 @@
         <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="O6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R6" t="n">
         <v>1.15</v>
@@ -1915,22 +1915,22 @@
         <v>6.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
         <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X6" t="n">
         <v>7.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
         <v>32</v>
@@ -1939,118 +1939,118 @@
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD6" t="n">
         <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL6" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO6" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP6" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6" t="n">
         <v>5.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AX6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY6" t="n">
+      <c r="BB6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC6" t="n">
         <v>10</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA6" t="n">
+      <c r="BD6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE6" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF6" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BJ6" t="n">
         <v>13</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN6" t="n">
         <v>4.9</v>
@@ -2062,41 +2062,41 @@
         <v>21</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV6" t="n">
         <v>55</v>
       </c>
       <c r="BW6" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="CA6" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
         <v>3</v>
@@ -2145,7 +2145,7 @@
         <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M7" t="n">
         <v>1.15</v>
@@ -2154,13 +2154,13 @@
         <v>2.26</v>
       </c>
       <c r="O7" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="R7" t="n">
         <v>1.13</v>
@@ -2169,19 +2169,19 @@
         <v>6.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V7" t="n">
         <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -2381,79 +2381,79 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="G8" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H8" t="n">
         <v>3.1</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P8" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="U8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="X8" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z8" t="n">
         <v>55</v>
       </c>
-      <c r="Z8" t="n">
-        <v>60</v>
-      </c>
       <c r="AA8" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AC8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
         <v>38</v>
@@ -2462,7 +2462,7 @@
         <v>34</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH8" t="n">
         <v>18</v>
@@ -2489,28 +2489,28 @@
         <v>13</v>
       </c>
       <c r="AP8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT8" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4</v>
       </c>
       <c r="AU8" t="n">
         <v>13</v>
       </c>
       <c r="AV8" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>25</v>
+        <v>4.2</v>
       </c>
       <c r="AX8" t="n">
         <v>20</v>
@@ -2525,7 +2525,7 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BC8" t="n">
         <v>13</v>
@@ -2534,19 +2534,19 @@
         <v>13.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.6</v>
@@ -2558,28 +2558,28 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN8" t="n">
         <v>7</v>
       </c>
       <c r="BO8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP8" t="n">
         <v>13</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BS8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU8" t="n">
         <v>4.3</v>
@@ -2588,23 +2588,23 @@
         <v>23</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX8" t="n">
         <v>21</v>
       </c>
       <c r="BY8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BZ8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="G9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I9" t="n">
         <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K9" t="n">
         <v>6</v>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="S9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="T9" t="n">
         <v>1.46</v>
@@ -2686,13 +2686,13 @@
         <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="X9" t="n">
         <v>55</v>
       </c>
       <c r="Y9" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="Z9" t="n">
         <v>120</v>
@@ -2704,16 +2704,16 @@
         <v>21</v>
       </c>
       <c r="AC9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
         <v>100</v>
       </c>
       <c r="AF9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG9" t="n">
         <v>12</v>
@@ -2722,10 +2722,10 @@
         <v>17.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
         <v>14.5</v>
@@ -2737,22 +2737,22 @@
         <v>95</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AO9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT9" t="n">
         <v>17.5</v>
@@ -2767,10 +2767,10 @@
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ9" t="n">
         <v>14.5</v>
@@ -2806,59 +2806,59 @@
         <v>9</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
         <v>5.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP9" t="n">
         <v>9.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR9" t="n">
         <v>16</v>
       </c>
       <c r="BS9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT9" t="n">
         <v>10.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="CA9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="G10" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.12</v>
@@ -2916,31 +2916,31 @@
         <v>17.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="R10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="S10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
         <v>1.25</v>
       </c>
       <c r="U10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X10" t="n">
         <v>170</v>
@@ -2961,10 +2961,10 @@
         <v>24</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
         <v>32</v>
@@ -2973,16 +2973,16 @@
         <v>18</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI10" t="n">
         <v>28</v>
       </c>
       <c r="AJ10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
         <v>18.5</v>
@@ -2991,13 +2991,13 @@
         <v>28</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AO10" t="n">
         <v>11.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>18</v>
@@ -3006,19 +3006,19 @@
         <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AT10" t="n">
         <v>17</v>
       </c>
       <c r="AU10" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AV10" t="n">
         <v>21</v>
       </c>
       <c r="AW10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX10" t="n">
         <v>13.5</v>
@@ -3036,7 +3036,7 @@
         <v>15.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD10" t="n">
         <v>16</v>
@@ -3045,49 +3045,49 @@
         <v>20</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="BG10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BJ10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP10" t="n">
         <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR10" t="n">
         <v>13</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU10" t="n">
         <v>6</v>
@@ -3096,23 +3096,23 @@
         <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX10" t="n">
         <v>19.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>2.52</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K11" t="n">
         <v>5.8</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
         <v>1.03</v>
       </c>
       <c r="P11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Q11" t="n">
         <v>1.11</v>
       </c>
       <c r="R11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T11" t="n">
         <v>1.18</v>
@@ -3203,10 +3203,10 @@
         <v>950</v>
       </c>
       <c r="Z11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA11" t="n">
         <v>500</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>900</v>
       </c>
       <c r="AB11" t="n">
         <v>950</v>
@@ -3215,19 +3215,19 @@
         <v>34</v>
       </c>
       <c r="AD11" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AE11" t="n">
         <v>170</v>
       </c>
       <c r="AF11" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AG11" t="n">
         <v>26</v>
       </c>
       <c r="AH11" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AI11" t="n">
         <v>42</v>
@@ -3239,134 +3239,134 @@
         <v>48</v>
       </c>
       <c r="AL11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM11" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AO11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AU11" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AV11" t="n">
         <v>9.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE11" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.6</v>
       </c>
       <c r="BF11" t="n">
         <v>4.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH11" t="n">
         <v>12.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BJ11" t="n">
         <v>8</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BN11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BP11" t="n">
         <v>16</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR11" t="n">
         <v>14</v>
       </c>
       <c r="BS11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV11" t="n">
         <v>16</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX11" t="n">
         <v>14</v>
       </c>
       <c r="BY11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.55</v>
       </c>
       <c r="G12" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="H12" t="n">
         <v>8</v>
@@ -3421,13 +3421,13 @@
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="O12" t="n">
         <v>1.53</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q12" t="n">
         <v>2.58</v>
@@ -3448,7 +3448,7 @@
         <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="X12" t="n">
         <v>10</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
         <v>1.67</v>
       </c>
       <c r="H13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
         <v>4.2</v>
@@ -3669,7 +3669,7 @@
         <v>4.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -3681,28 +3681,28 @@
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
         <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
@@ -3711,7 +3711,7 @@
         <v>25</v>
       </c>
       <c r="Z13" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AA13" t="n">
         <v>700</v>
@@ -3726,7 +3726,7 @@
         <v>29</v>
       </c>
       <c r="AE13" t="n">
-        <v>700</v>
+        <v>240</v>
       </c>
       <c r="AF13" t="n">
         <v>10.5</v>
@@ -3741,58 +3741,58 @@
         <v>700</v>
       </c>
       <c r="AJ13" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AK13" t="n">
         <v>65</v>
       </c>
       <c r="AL13" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO13" t="n">
         <v>700</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
         <v>13.5</v>
@@ -3801,22 +3801,22 @@
         <v>14.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ13" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
         <v>3.45</v>
       </c>
       <c r="BP13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3849,10 +3849,10 @@
         <v>10</v>
       </c>
       <c r="BT13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3867,14 +3867,14 @@
         <v>13</v>
       </c>
       <c r="BZ13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -3905,79 +3905,79 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="G14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>2.82</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="L14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="M14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N14" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="O14" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="P14" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="V14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AA14" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC14" t="n">
         <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE14" t="n">
         <v>110</v>
@@ -3986,34 +3986,34 @@
         <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH14" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ14" t="n">
         <v>32</v>
       </c>
       <c r="AK14" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AM14" t="n">
         <v>320</v>
       </c>
       <c r="AN14" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AO14" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ14" t="n">
         <v>10</v>
@@ -4022,16 +4022,16 @@
         <v>25</v>
       </c>
       <c r="AS14" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU14" t="n">
         <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW14" t="n">
         <v>11.5</v>
@@ -4046,43 +4046,43 @@
         <v>26</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BC14" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="BD14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
         <v>12</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>32</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>12.5</v>
       </c>
       <c r="BN14" t="n">
         <v>4.8</v>
@@ -4100,25 +4100,25 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU14" t="n">
         <v>5.6</v>
       </c>
       <c r="BV14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -4159,67 +4159,67 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U15" t="n">
         <v>2.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="X15" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="n">
         <v>95</v>
@@ -4228,16 +4228,16 @@
         <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
         <v>70</v>
       </c>
       <c r="AF15" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
         <v>15.5</v>
@@ -4258,10 +4258,10 @@
         <v>60</v>
       </c>
       <c r="AM15" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO15" t="n">
         <v>80</v>
@@ -4270,13 +4270,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR15" t="n">
-        <v>19</v>
+        <v>5.9</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT15" t="n">
         <v>6.2</v>
@@ -4285,61 +4285,61 @@
         <v>6</v>
       </c>
       <c r="AV15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB15" t="n">
         <v>6</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7.6</v>
       </c>
       <c r="BC15" t="n">
         <v>18</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="BF15" t="n">
         <v>15.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO15" t="n">
         <v>4.1</v>
@@ -4354,35 +4354,35 @@
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>6.2</v>
+        <v>3.85</v>
       </c>
       <c r="BT15" t="n">
         <v>6.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
         <v>4.8</v>
@@ -4425,7 +4425,7 @@
         <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
         <v>3.35</v>
@@ -4440,7 +4440,7 @@
         <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P16" t="n">
         <v>1.64</v>
@@ -4455,7 +4455,7 @@
         <v>4.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U16" t="n">
         <v>1.83</v>
@@ -4464,7 +4464,7 @@
         <v>1.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X16" t="n">
         <v>9.800000000000001</v>
@@ -4473,7 +4473,7 @@
         <v>16</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AA16" t="n">
         <v>150</v>
@@ -4518,28 +4518,28 @@
         <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ16" t="n">
         <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>26</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT16" t="n">
         <v>6.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AW16" t="n">
         <v>9.800000000000001</v>
@@ -4551,10 +4551,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
@@ -4563,7 +4563,7 @@
         <v>22</v>
       </c>
       <c r="BD16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BE16" t="n">
         <v>10</v>
@@ -4572,7 +4572,7 @@
         <v>19</v>
       </c>
       <c r="BG16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH16" t="n">
         <v>2.88</v>
@@ -4605,7 +4605,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS16" t="n">
         <v>11.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
         <v>2.56</v>
       </c>
       <c r="H17" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.53</v>
@@ -4694,7 +4694,7 @@
         <v>2.98</v>
       </c>
       <c r="O17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P17" t="n">
         <v>1.65</v>
@@ -4706,7 +4706,7 @@
         <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
         <v>2</v>
@@ -4715,19 +4715,19 @@
         <v>1.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
         <v>1.64</v>
       </c>
       <c r="X17" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AA17" t="n">
         <v>85</v>
@@ -4739,13 +4739,13 @@
         <v>7.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
         <v>50</v>
       </c>
       <c r="AF17" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG17" t="n">
         <v>12.5</v>
@@ -4754,7 +4754,7 @@
         <v>970</v>
       </c>
       <c r="AI17" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ17" t="n">
         <v>40</v>
@@ -4763,25 +4763,25 @@
         <v>34</v>
       </c>
       <c r="AL17" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN17" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AO17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="AS17" t="n">
         <v>55</v>
@@ -4808,7 +4808,7 @@
         <v>19.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>44</v>
+        <v>12.5</v>
       </c>
       <c r="BB17" t="n">
         <v>32</v>
@@ -4817,22 +4817,22 @@
         <v>28</v>
       </c>
       <c r="BD17" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BE17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF17" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BG17" t="n">
-        <v>12.5</v>
+        <v>48</v>
       </c>
       <c r="BH17" t="n">
         <v>2.88</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.35</v>
+        <v>2.72</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="I2" t="n">
-        <v>2.24</v>
+        <v>2.72</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.34</v>
@@ -890,197 +890,197 @@
         <v>2.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
         <v>2.84</v>
       </c>
       <c r="T2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AB2" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AF2" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AG2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH2" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH2" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AI2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL2" t="n">
         <v>32</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>40</v>
       </c>
       <c r="AM2" t="n">
         <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX2" t="n">
         <v>18</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AY2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>11.5</v>
       </c>
       <c r="BH2" t="n">
         <v>3.95</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BL2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM2" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BR2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BS2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BY2" t="n">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>19</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -1111,100 +1111,100 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="J3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K3" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="T3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U3" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AF3" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>32</v>
@@ -1213,19 +1213,19 @@
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AP3" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
         <v>50</v>
@@ -1237,104 +1237,104 @@
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
         <v>27</v>
       </c>
       <c r="BE3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BH3" t="n">
         <v>4</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>12.5</v>
       </c>
-      <c r="BN3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BR3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV3" t="n">
         <v>25</v>
       </c>
-      <c r="BS3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>24</v>
-      </c>
       <c r="BW3" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="BZ3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -1365,31 +1365,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I4" t="n">
         <v>2.26</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.13</v>
@@ -1401,43 +1401,43 @@
         <v>1.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S4" t="n">
         <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X4" t="n">
         <v>36</v>
       </c>
       <c r="Y4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z4" t="n">
         <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC4" t="n">
         <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>20</v>
@@ -1455,22 +1455,22 @@
         <v>23</v>
       </c>
       <c r="AJ4" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AK4" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AL4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
         <v>14.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP4" t="n">
         <v>30</v>
@@ -1479,25 +1479,25 @@
         <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV4" t="n">
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY4" t="n">
         <v>13</v>
@@ -1509,7 +1509,7 @@
         <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BC4" t="n">
         <v>25</v>
@@ -1521,37 +1521,37 @@
         <v>34</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN4" t="n">
         <v>7.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BP4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ4" t="n">
         <v>8.6</v>
@@ -1560,19 +1560,19 @@
         <v>23</v>
       </c>
       <c r="BS4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
         <v>13.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>19</v>
@@ -1581,14 +1581,14 @@
         <v>8.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA4" t="n">
         <v>6.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -1619,61 +1619,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="H5" t="n">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="W5" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="X5" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1727,82 +1727,82 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.6</v>
+        <v>1.81</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.54</v>
+        <v>1.78</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.52</v>
+        <v>1.84</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.8</v>
+        <v>1.81</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.56</v>
+        <v>1.81</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.54</v>
+        <v>4.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.54</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.52</v>
+        <v>1.87</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.56</v>
+        <v>1.81</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
         <v>1.04</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.8</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1814,19 +1814,19 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -1873,88 +1873,88 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="G6" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="O6" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="P6" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="X6" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AF6" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>28</v>
@@ -1963,140 +1963,140 @@
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AK6" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AO6" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AP6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU6" t="n">
         <v>6.2</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="AV6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA6" t="n">
+      <c r="BF6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH6" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="BJ6" t="n">
         <v>13</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BP6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR6" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ6" t="n">
         <v>50</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>100</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>75</v>
       </c>
       <c r="CA6" t="n">
         <v>8.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J7" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L7" t="n">
         <v>1.65</v>
@@ -2154,13 +2154,13 @@
         <v>2.26</v>
       </c>
       <c r="O7" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
         <v>1.13</v>
@@ -2172,16 +2172,16 @@
         <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
         <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
@@ -2235,76 +2235,76 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.18</v>
+        <v>5.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.14</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.16</v>
+        <v>4.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.18</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="AZ7" t="n">
         <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.16</v>
+        <v>6.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
@@ -2316,41 +2316,41 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>1.04</v>
       </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I8" t="n">
         <v>3.75</v>
@@ -2423,19 +2423,19 @@
         <v>1.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="U8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Y8" t="n">
         <v>50</v>
@@ -2459,7 +2459,7 @@
         <v>38</v>
       </c>
       <c r="AF8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG8" t="n">
         <v>17.5</v>
@@ -2477,46 +2477,46 @@
         <v>22</v>
       </c>
       <c r="AL8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AO8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AU8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV8" t="n">
         <v>15.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>12</v>
@@ -2525,19 +2525,19 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD8" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="BG8" t="n">
         <v>8.199999999999999</v>
@@ -2600,11 +2600,11 @@
         <v>8</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G9" t="n">
         <v>1.57</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I9" t="n">
         <v>6</v>
@@ -2650,37 +2650,37 @@
         <v>5.4</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="R9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="T9" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="V9" t="n">
         <v>1.2</v>
@@ -2689,176 +2689,176 @@
         <v>2.74</v>
       </c>
       <c r="X9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="Y9" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Z9" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AA9" t="n">
         <v>700</v>
       </c>
       <c r="AB9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AC9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF9" t="n">
         <v>15.5</v>
       </c>
-      <c r="AD9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP9" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>12.5</v>
       </c>
       <c r="AR9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU9" t="n">
         <v>12</v>
       </c>
-      <c r="AS9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>13</v>
-      </c>
       <c r="AV9" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
         <v>23</v>
       </c>
       <c r="BB9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BG9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BJ9" t="n">
         <v>9</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN9" t="n">
         <v>5.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP9" t="n">
         <v>9.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BR9" t="n">
         <v>16</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -2889,31 +2889,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="G10" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K10" t="n">
         <v>6.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="O10" t="n">
         <v>1.04</v>
@@ -2925,10 +2925,10 @@
         <v>1.16</v>
       </c>
       <c r="R10" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T10" t="n">
         <v>1.25</v>
@@ -2937,49 +2937,49 @@
         <v>4.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W10" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="X10" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="Y10" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="Z10" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA10" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AC10" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AD10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH10" t="n">
         <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>28</v>
+        <v>420</v>
       </c>
       <c r="AJ10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AK10" t="n">
         <v>18</v>
@@ -2991,13 +2991,13 @@
         <v>28</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AO10" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AP10" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
         <v>18</v>
@@ -3006,70 +3006,70 @@
         <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AT10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC10" t="n">
         <v>15.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BE10" t="n">
         <v>20</v>
       </c>
       <c r="BF10" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BJ10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO10" t="n">
         <v>5.3</v>
@@ -3078,41 +3078,41 @@
         <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR10" t="n">
         <v>13</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT10" t="n">
         <v>11</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV10" t="n">
         <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BY10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.38</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H11" t="n">
         <v>2.36</v>
@@ -3155,7 +3155,7 @@
         <v>2.52</v>
       </c>
       <c r="J11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K11" t="n">
         <v>5.8</v>
@@ -3167,31 +3167,31 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="O11" t="n">
         <v>1.03</v>
       </c>
       <c r="P11" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="S11" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T11" t="n">
         <v>1.18</v>
       </c>
       <c r="U11" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W11" t="n">
         <v>1.64</v>
@@ -3200,7 +3200,7 @@
         <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z11" t="n">
         <v>100</v>
@@ -3209,25 +3209,25 @@
         <v>500</v>
       </c>
       <c r="AB11" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC11" t="n">
         <v>34</v>
       </c>
       <c r="AD11" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AE11" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AF11" t="n">
         <v>100</v>
       </c>
       <c r="AG11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI11" t="n">
         <v>42</v>
@@ -3242,55 +3242,55 @@
         <v>24</v>
       </c>
       <c r="AM11" t="n">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AO11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="AW11" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AZ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA11" t="n">
         <v>14</v>
       </c>
-      <c r="BA11" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BB11" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC11" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BD11" t="n">
         <v>17</v>
@@ -3299,34 +3299,34 @@
         <v>10.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BI11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BJ11" t="n">
         <v>8</v>
       </c>
       <c r="BK11" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP11" t="n">
         <v>16</v>
@@ -3341,10 +3341,10 @@
         <v>6.8</v>
       </c>
       <c r="BT11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV11" t="n">
         <v>16</v>
@@ -3359,14 +3359,14 @@
         <v>6.8</v>
       </c>
       <c r="BZ11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -3397,64 +3397,64 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="G12" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="M12" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="P12" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.54</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
         <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="Z12" t="n">
         <v>85</v>
@@ -3463,112 +3463,112 @@
         <v>700</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AE12" t="n">
         <v>700</v>
       </c>
       <c r="AF12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AI12" t="n">
         <v>700</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>410</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
         <v>6</v>
       </c>
       <c r="AR12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS12" t="n">
         <v>8</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AT12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY12" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AT12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD12" t="n">
         <v>7.2</v>
       </c>
-      <c r="AW12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD12" t="n">
+      <c r="BE12" t="n">
         <v>8</v>
       </c>
-      <c r="BE12" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF12" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="BJ12" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3577,40 +3577,40 @@
         <v>10.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BO12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="G13" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.34</v>
@@ -3675,43 +3675,43 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="Z13" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="n">
         <v>700</v>
@@ -3720,161 +3720,161 @@
         <v>9.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE13" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AF13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
         <v>700</v>
       </c>
       <c r="AJ13" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AK13" t="n">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="AL13" t="n">
-        <v>160</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AP13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="AR13" t="n">
         <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX13" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>9</v>
       </c>
       <c r="AY13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC13" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>14.5</v>
       </c>
       <c r="BD13" t="n">
         <v>15.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BN13" t="n">
         <v>4.3</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BP13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT13" t="n">
         <v>10</v>
       </c>
-      <c r="BQ13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BU13" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BZ13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -3908,13 +3908,13 @@
         <v>2.18</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H14" t="n">
         <v>4.6</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>2.82</v>
@@ -3935,7 +3935,7 @@
         <v>1.64</v>
       </c>
       <c r="P14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q14" t="n">
         <v>2.98</v>
@@ -3944,16 +3944,16 @@
         <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W14" t="n">
         <v>1.78</v>
@@ -3965,13 +3965,13 @@
         <v>12.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA14" t="n">
         <v>140</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC14" t="n">
         <v>7</v>
@@ -4001,7 +4001,7 @@
         <v>36</v>
       </c>
       <c r="AL14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="n">
         <v>320</v>
@@ -4010,7 +4010,7 @@
         <v>36</v>
       </c>
       <c r="AO14" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AP14" t="n">
         <v>6.6</v>
@@ -4022,19 +4022,19 @@
         <v>25</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
         <v>5.7</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
         <v>18.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
         <v>10</v>
@@ -4046,73 +4046,73 @@
         <v>26</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
         <v>24</v>
       </c>
       <c r="BC14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF14" t="n">
         <v>24</v>
       </c>
       <c r="BG14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="n">
         <v>2.64</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ14" t="n">
         <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN14" t="n">
         <v>4.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ14" t="n">
         <v>8</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT14" t="n">
         <v>7.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -4159,64 +4159,64 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="H15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.55</v>
       </c>
-      <c r="I15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
         <v>3.3</v>
       </c>
-      <c r="K15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
       <c r="T15" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="U15" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="X15" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Z15" t="n">
         <v>34</v>
@@ -4225,164 +4225,164 @@
         <v>95</v>
       </c>
       <c r="AB15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AF15" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
         <v>24</v>
       </c>
       <c r="AI15" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK15" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AM15" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AO15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.9</v>
+        <v>16.5</v>
       </c>
       <c r="AS15" t="n">
         <v>6.8</v>
       </c>
       <c r="AT15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW15" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AX15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA15" t="n">
         <v>6</v>
       </c>
-      <c r="AV15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW15" t="n">
+      <c r="BB15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG15" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA15" t="n">
+      <c r="BH15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>3.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
         <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
         <v>3.35</v>
@@ -4455,7 +4455,7 @@
         <v>4.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U16" t="n">
         <v>1.83</v>
@@ -4464,19 +4464,19 @@
         <v>1.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y16" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB16" t="n">
         <v>7</v>
@@ -4485,13 +4485,13 @@
         <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AF16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -4506,7 +4506,7 @@
         <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AL16" t="n">
         <v>55</v>
@@ -4518,43 +4518,43 @@
         <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AP16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ16" t="n">
         <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="AX16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="BA16" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
@@ -4566,13 +4566,13 @@
         <v>20</v>
       </c>
       <c r="BE16" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BF16" t="n">
         <v>19</v>
       </c>
       <c r="BG16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BH16" t="n">
         <v>2.88</v>
@@ -4596,7 +4596,7 @@
         <v>4.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BP16" t="n">
         <v>16</v>
@@ -4605,7 +4605,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
         <v>11.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>3.45</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
         <v>3.3</v>
@@ -4691,7 +4691,7 @@
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O17" t="n">
         <v>1.48</v>
@@ -4712,7 +4712,7 @@
         <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V17" t="n">
         <v>1.41</v>
@@ -4721,40 +4721,40 @@
         <v>1.64</v>
       </c>
       <c r="X17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AA17" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC17" t="n">
         <v>7.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF17" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AI17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
         <v>40</v>
@@ -4766,7 +4766,7 @@
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AN17" t="n">
         <v>46</v>
@@ -4778,10 +4778,10 @@
         <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS17" t="n">
         <v>55</v>
@@ -4808,89 +4808,89 @@
         <v>19.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB17" t="n">
         <v>32</v>
       </c>
       <c r="BC17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD17" t="n">
         <v>40</v>
       </c>
       <c r="BE17" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BF17" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BG17" t="n">
         <v>48</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BI17" t="n">
         <v>2.66</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.4</v>
+        <v>15</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR17" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS17" t="n">
-        <v>2.24</v>
+        <v>11.5</v>
       </c>
       <c r="BT17" t="n">
         <v>6.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>42</v>
+      </c>
+      <c r="CA17" t="n">
         <v>11.5</v>
       </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>2.26</v>
-      </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="G3" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="H3" t="n">
-        <v>3.65</v>
+        <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>110</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.32</v>
+        <v>1.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="S3" t="n">
-        <v>2.86</v>
+        <v>1.11</v>
       </c>
       <c r="T3" t="n">
-        <v>1.63</v>
+        <v>5.7</v>
       </c>
       <c r="U3" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>15</v>
+        <v>1.12</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15.5</v>
+        <v>250</v>
       </c>
       <c r="AR3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AS3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AT3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AU3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA3" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>36</v>
-      </c>
       <c r="BB3" t="n">
-        <v>24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>27</v>
+        <v>1.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>60</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>27</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>7.8</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>2.26</v>
+        <v>1.53</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.79</v>
+        <v>2.88</v>
       </c>
       <c r="W4" t="n">
-        <v>1.45</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>23</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP4" t="n">
         <v>29</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AQ4" t="n">
         <v>29</v>
       </c>
-      <c r="AM4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>18</v>
-      </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AS4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AW4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY4" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="BA4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="BC4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BD4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BE4" t="n">
-        <v>34</v>
+        <v>7.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.26</v>
+        <v>1.47</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5</v>
+        <v>1.51</v>
       </c>
       <c r="J5" t="n">
-        <v>2.84</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.1</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.26</v>
-      </c>
       <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>790</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW5" t="n">
         <v>14</v>
       </c>
-      <c r="Y5" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH5" t="n">
+      <c r="AX5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>960</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BX5" t="n">
         <v>950</v>
       </c>
-      <c r="AI5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY5" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O6" t="n">
         <v>2.04</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.56</v>
-      </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="S6" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="X6" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AE6" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AF6" t="n">
         <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AH6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>350</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>480</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR6" t="n">
         <v>28</v>
       </c>
-      <c r="AI6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK6" t="n">
+      <c r="AS6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>40</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>200</v>
+      </c>
+      <c r="BB6" t="n">
         <v>32</v>
       </c>
-      <c r="AL6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN6" t="n">
+      <c r="BC6" t="n">
+        <v>48</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>150</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>60</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>190</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>32</v>
       </c>
-      <c r="AO6" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ6" t="n">
+      <c r="BK6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>46</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>910</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>95</v>
+      </c>
+      <c r="BT6" t="n">
         <v>10</v>
       </c>
-      <c r="AR6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD6" t="n">
+      <c r="BU6" t="n">
         <v>7.6</v>
       </c>
-      <c r="BE6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.6</v>
+        <v>75</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
-        <v>50</v>
+        <v>960</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.4</v>
+        <v>140</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="G7" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="K7" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.65</v>
+        <v>2.46</v>
       </c>
       <c r="M7" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="N7" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="O7" t="n">
-        <v>1.64</v>
+        <v>2.12</v>
       </c>
       <c r="P7" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="S7" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="X7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>270</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>90</v>
       </c>
-      <c r="Y7" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AK7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>240</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>260</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>38</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>29</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>65</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>910</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>120</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX7" t="n">
         <v>950</v>
       </c>
-      <c r="AI7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>19.5</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.1</v>
+        <v>18.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -2381,73 +2381,73 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="G8" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="K8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.07</v>
       </c>
       <c r="P8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="S8" t="n">
         <v>1.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="U8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="X8" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Y8" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="Z8" t="n">
         <v>55</v>
       </c>
       <c r="AA8" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AB8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AC8" t="n">
         <v>21</v>
@@ -2459,10 +2459,10 @@
         <v>38</v>
       </c>
       <c r="AF8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG8" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH8" t="n">
         <v>18</v>
@@ -2471,46 +2471,46 @@
         <v>32</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM8" t="n">
         <v>38</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="AO8" t="n">
         <v>13.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AX8" t="n">
         <v>21</v>
@@ -2519,37 +2519,37 @@
         <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.9</v>
+        <v>22</v>
       </c>
       <c r="BC8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD8" t="n">
         <v>16</v>
       </c>
       <c r="BE8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF8" t="n">
         <v>3.9</v>
       </c>
-      <c r="BF8" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BG8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH8" t="n">
         <v>7.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BJ8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK8" t="n">
         <v>6</v>
@@ -2558,53 +2558,53 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>22</v>
+      </c>
+      <c r="BY8" t="n">
         <v>7</v>
       </c>
-      <c r="BO8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>23</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BZ8" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="CA8" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
         <v>5.4</v>
       </c>
       <c r="K9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.2</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.11</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="R9" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="S9" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="T9" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="U9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W9" t="n">
         <v>2.78</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.74</v>
-      </c>
       <c r="X9" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="Y9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Z9" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="AA9" t="n">
         <v>700</v>
       </c>
       <c r="AB9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
         <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM9" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
         <v>4.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP9" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="AR9" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
         <v>10.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV9" t="n">
         <v>20</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
         <v>19.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF9" t="n">
         <v>3.95</v>
       </c>
       <c r="BG9" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="BH9" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BI9" t="n">
         <v>4.8</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.5</v>
+        <v>2.34</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>11</v>
+        <v>2.34</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.6</v>
+        <v>1.87</v>
       </c>
       <c r="BR9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.4</v>
+        <v>2.34</v>
       </c>
       <c r="BT9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.8</v>
+        <v>1.92</v>
       </c>
       <c r="BV9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>10</v>
+        <v>2.34</v>
       </c>
       <c r="BX9" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.6</v>
+        <v>2.34</v>
       </c>
       <c r="BZ9" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.2</v>
+        <v>2.34</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -2889,193 +2889,193 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="G10" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="H10" t="n">
         <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="K10" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X10" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG10" t="n">
         <v>16</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="P10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="X10" t="n">
-        <v>140</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>160</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="AH10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI10" t="n">
         <v>29</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>420</v>
       </c>
       <c r="AJ10" t="n">
         <v>55</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL10" t="n">
         <v>18.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AO10" t="n">
         <v>14</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU10" t="n">
         <v>18</v>
       </c>
-      <c r="AR10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>20</v>
-      </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>14.5</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BA10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC10" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>15.5</v>
       </c>
       <c r="BD10" t="n">
         <v>15.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="BG10" t="n">
         <v>10.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BI10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BJ10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO10" t="n">
         <v>5.3</v>
       </c>
       <c r="BP10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ10" t="n">
         <v>6.2</v>
@@ -3084,35 +3084,35 @@
         <v>13</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
         <v>11</v>
       </c>
       <c r="BU10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV10" t="n">
         <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX10" t="n">
         <v>20</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="G11" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
         <v>5.8</v>
@@ -3167,106 +3167,106 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="O11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="P11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="R11" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="S11" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="U11" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>950</v>
+        <v>140</v>
       </c>
       <c r="Y11" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="Z11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB11" t="n">
         <v>100</v>
       </c>
-      <c r="AA11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>500</v>
-      </c>
       <c r="AC11" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AD11" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="AE11" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AF11" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AG11" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AH11" t="n">
         <v>15.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="AJ11" t="n">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AK11" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AM11" t="n">
         <v>24</v>
       </c>
-      <c r="AM11" t="n">
-        <v>200</v>
-      </c>
       <c r="AN11" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AO11" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.4</v>
+        <v>27</v>
       </c>
       <c r="AR11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.4</v>
+        <v>27</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="AV11" t="n">
         <v>18</v>
@@ -3275,98 +3275,98 @@
         <v>21</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BC11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
         <v>17</v>
       </c>
       <c r="BE11" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BH11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BJ11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>26</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>8</v>
       </c>
-      <c r="BK11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BR11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BY11" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ11" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="CA11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -3397,64 +3397,64 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="G12" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="H12" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O12" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W12" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z12" t="n">
         <v>85</v>
@@ -3463,10 +3463,10 @@
         <v>700</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
         <v>36</v>
@@ -3478,10 +3478,10 @@
         <v>8.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI12" t="n">
         <v>700</v>
@@ -3490,43 +3490,43 @@
         <v>15.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AU12" t="n">
         <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX12" t="n">
         <v>6.6</v>
@@ -3538,79 +3538,79 @@
         <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC12" t="n">
         <v>16</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF12" t="n">
         <v>9.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="BI12" t="n">
         <v>2.6</v>
       </c>
       <c r="BJ12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK12" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO12" t="n">
         <v>3.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT12" t="n">
         <v>12</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.57</v>
       </c>
       <c r="G13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H13" t="n">
         <v>6.2</v>
@@ -3663,7 +3663,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K13" t="n">
         <v>4.9</v>
@@ -3684,7 +3684,7 @@
         <v>2.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R13" t="n">
         <v>1.49</v>
@@ -3693,16 +3693,16 @@
         <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
         <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
@@ -3720,7 +3720,7 @@
         <v>9.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
         <v>28</v>
@@ -3729,7 +3729,7 @@
         <v>700</v>
       </c>
       <c r="AF13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
@@ -3753,13 +3753,13 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO13" t="n">
         <v>110</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>21</v>
@@ -3768,10 +3768,10 @@
         <v>22</v>
       </c>
       <c r="AS13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU13" t="n">
         <v>9.4</v>
@@ -3789,7 +3789,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
         <v>11</v>
@@ -3798,22 +3798,22 @@
         <v>13</v>
       </c>
       <c r="BC13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD13" t="n">
         <v>15.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI13" t="n">
         <v>3.15</v>
@@ -3822,59 +3822,59 @@
         <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN13" t="n">
         <v>4.3</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BR13" t="n">
         <v>23</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX13" t="n">
         <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ13" t="n">
         <v>15.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -3908,31 +3908,31 @@
         <v>2.18</v>
       </c>
       <c r="G14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
         <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K14" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="L14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
         <v>1.16</v>
       </c>
       <c r="N14" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="O14" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P14" t="n">
         <v>1.47</v>
@@ -3944,22 +3944,22 @@
         <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="U14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Y14" t="n">
         <v>12.5</v>
@@ -3968,7 +3968,7 @@
         <v>36</v>
       </c>
       <c r="AA14" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AB14" t="n">
         <v>6.6</v>
@@ -3980,10 +3980,10 @@
         <v>23</v>
       </c>
       <c r="AE14" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG14" t="n">
         <v>15</v>
@@ -3995,7 +3995,7 @@
         <v>140</v>
       </c>
       <c r="AJ14" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK14" t="n">
         <v>36</v>
@@ -4004,10 +4004,10 @@
         <v>75</v>
       </c>
       <c r="AM14" t="n">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AN14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO14" t="n">
         <v>170</v>
@@ -4022,19 +4022,19 @@
         <v>25</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW14" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AX14" t="n">
         <v>10</v>
@@ -4043,28 +4043,28 @@
         <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BB14" t="n">
         <v>24</v>
       </c>
       <c r="BC14" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BD14" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF14" t="n">
         <v>24</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH14" t="n">
         <v>2.64</v>
@@ -4088,7 +4088,7 @@
         <v>4.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP14" t="n">
         <v>20</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -4159,64 +4159,64 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="G15" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="J15" t="n">
         <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="R15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.4</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.32</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
         <v>34</v>
@@ -4225,164 +4225,164 @@
         <v>95</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AF15" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AJ15" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL15" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM15" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN15" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AP15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="AR15" t="n">
         <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.8</v>
+        <v>38</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
         <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT15" t="n">
         <v>6.6</v>
       </c>
-      <c r="BD15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK15" t="n">
+      <c r="BU15" t="n">
         <v>5.5</v>
       </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -4422,10 +4422,10 @@
         <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
         <v>3.35</v>
@@ -4452,7 +4452,7 @@
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T16" t="n">
         <v>2.14</v>
@@ -4470,7 +4470,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Z16" t="n">
         <v>36</v>
@@ -4488,7 +4488,7 @@
         <v>26</v>
       </c>
       <c r="AE16" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF16" t="n">
         <v>11</v>
@@ -4506,13 +4506,13 @@
         <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL16" t="n">
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN16" t="n">
         <v>22</v>
@@ -4521,7 +4521,7 @@
         <v>130</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ16" t="n">
         <v>12</v>
@@ -4530,7 +4530,7 @@
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="AT16" t="n">
         <v>6.4</v>
@@ -4542,13 +4542,13 @@
         <v>18</v>
       </c>
       <c r="AW16" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
         <v>22</v>
@@ -4566,13 +4566,13 @@
         <v>20</v>
       </c>
       <c r="BE16" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BF16" t="n">
         <v>19</v>
       </c>
       <c r="BG16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH16" t="n">
         <v>2.88</v>
@@ -4596,7 +4596,7 @@
         <v>4.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BP16" t="n">
         <v>16</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G17" t="n">
         <v>2.56</v>
@@ -4676,10 +4676,10 @@
         <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
         <v>3.3</v>
@@ -4706,7 +4706,7 @@
         <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T17" t="n">
         <v>2</v>
@@ -4721,7 +4721,7 @@
         <v>1.64</v>
       </c>
       <c r="X17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="n">
         <v>10.5</v>
@@ -4742,10 +4742,10 @@
         <v>14.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
@@ -4757,7 +4757,7 @@
         <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK17" t="n">
         <v>34</v>
@@ -4769,19 +4769,19 @@
         <v>180</v>
       </c>
       <c r="AN17" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AO17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP17" t="n">
         <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS17" t="n">
         <v>55</v>
@@ -4790,16 +4790,16 @@
         <v>7.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV17" t="n">
         <v>13.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY17" t="n">
         <v>11</v>
@@ -4808,7 +4808,7 @@
         <v>19.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>15.5</v>
+        <v>42</v>
       </c>
       <c r="BB17" t="n">
         <v>32</v>
@@ -4817,10 +4817,10 @@
         <v>29</v>
       </c>
       <c r="BD17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BF17" t="n">
         <v>29</v>
@@ -4838,13 +4838,13 @@
         <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN17" t="n">
         <v>5.3</v>
@@ -4856,41 +4856,41 @@
         <v>22</v>
       </c>
       <c r="BQ17" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BR17" t="n">
         <v>40</v>
       </c>
       <c r="BS17" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU17" t="n">
         <v>5.6</v>
       </c>
       <c r="BV17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ17" t="n">
         <v>42</v>
       </c>
       <c r="CA17" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Maranhao</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1.83</v>
+        <v>1.07</v>
       </c>
       <c r="H2" t="n">
-        <v>7.2</v>
+        <v>330</v>
       </c>
       <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>110</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S2" t="n">
+        <v>110</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY2" t="n">
         <v>8</v>
       </c>
-      <c r="J2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="AZ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE2" t="n">
         <v>10</v>
       </c>
-      <c r="T2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>490</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>310</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>560</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU2" t="n">
+      <c r="BF2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>46</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>120</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>25</v>
-      </c>
       <c r="BG2" t="n">
-        <v>290</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -1102,246 +1102,246 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.14</v>
+        <v>7.8</v>
       </c>
       <c r="G3" t="n">
-        <v>2.24</v>
+        <v>25</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>19.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8</v>
+        <v>1.13</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.17</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.45</v>
-      </c>
       <c r="Q3" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="S3" t="n">
-        <v>6.8</v>
+        <v>80</v>
       </c>
       <c r="T3" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.2</v>
+        <v>1.21</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AE3" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT3" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AU3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>6</v>
       </c>
-      <c r="AV3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>26</v>
-      </c>
       <c r="BA3" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>25</v>
+        <v>6.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>29</v>
+        <v>6.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>60</v>
+        <v>6.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="BG3" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,244 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>1.29</v>
       </c>
       <c r="G4" t="n">
-        <v>2.34</v>
+        <v>1.31</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7</v>
+        <v>26</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>32</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="O4" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="P4" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.48</v>
+        <v>4.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="S4" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.84</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.75</v>
+        <v>4.2</v>
       </c>
       <c r="X4" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.6</v>
+        <v>2.72</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.5</v>
+        <v>46</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>440</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>4.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="AK4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV4" t="n">
         <v>32</v>
       </c>
-      <c r="AL4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AW4" t="n">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="AX4" t="n">
-        <v>12</v>
+        <v>4.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="BA4" t="n">
+        <v>280</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>170</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>350</v>
+      </c>
+      <c r="BF4" t="n">
         <v>60</v>
       </c>
-      <c r="BB4" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>25</v>
-      </c>
       <c r="BG4" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -1610,493 +1610,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.97</v>
+        <v>1.27</v>
       </c>
       <c r="G5" t="n">
-        <v>1.98</v>
+        <v>1.3</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>25</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>26</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>2.62</v>
       </c>
       <c r="S5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
         <v>4.9</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AL5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM5" t="n">
         <v>80</v>
       </c>
-      <c r="AF5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>180</v>
-      </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AS5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AW5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>2.54</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="BA5" t="n">
         <v>30</v>
       </c>
       <c r="BB5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
-        <v>22</v>
+        <v>4.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="BE5" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="BF5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Londrina</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Avai</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>120</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>42</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>13</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
